--- a/internal_doc/01.需求特性/版本特性列表.xlsx
+++ b/internal_doc/01.需求特性/版本特性列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="90" windowWidth="23760" windowHeight="11190"/>
+    <workbookView xWindow="120" yWindow="90" windowWidth="15480" windowHeight="11190"/>
   </bookViews>
   <sheets>
     <sheet name="版本特性表" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="116">
   <si>
     <t>内容项</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -350,10 +350,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>与spark集成</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Simple SQL</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -403,6 +399,86 @@
   </si>
   <si>
     <t>资料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白皮书</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>信息中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开发指南</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与Databus集成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>定期巡检</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bug追踪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>漏洞推送</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xxx人天的现场支持+24x7电话支持，SLA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>收费定制化开发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>免费+收费现场升级支持</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提供企业账号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>免费+收费应用架构咨询，POC，部署等</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提供企业账号以及推送服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xxx人天的巡检服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMTP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库前滚+日志归档</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>读写分离</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与spark（spark sql\spark stream）集成</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -829,73 +905,73 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1195,7 +1271,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.5" customWidth="1"/>
@@ -1223,810 +1299,918 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="14.25" thickTop="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="18" t="s">
         <v>16</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="10"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="34"/>
+      <c r="A3" s="25"/>
       <c r="B3" s="22"/>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="18" t="s">
         <v>17</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="13"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="34"/>
+      <c r="A4" s="25"/>
       <c r="B4" s="22"/>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="17" t="s">
         <v>18</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="13"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="34"/>
+      <c r="A5" s="25"/>
       <c r="B5" s="22"/>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="13"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="34"/>
+      <c r="A6" s="25"/>
       <c r="B6" s="23"/>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="12"/>
+      <c r="D6" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="E6" s="13"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="34"/>
-      <c r="B7" s="26" t="s">
+      <c r="A7" s="25"/>
+      <c r="B7" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="12"/>
+      <c r="D7" s="12" t="s">
+        <v>97</v>
+      </c>
       <c r="E7" s="13"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="34"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="29" t="s">
+      <c r="A8" s="25"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="12"/>
+      <c r="D8" s="12" t="s">
+        <v>97</v>
+      </c>
       <c r="E8" s="13"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="34"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="27" t="s">
+      <c r="A9" s="25"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="12"/>
+      <c r="D9" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="E9" s="13"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="34"/>
-      <c r="B10" s="20" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="21" t="s">
-        <v>86</v>
+      <c r="C10" s="17" t="s">
+        <v>85</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="13"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="34"/>
+      <c r="A11" s="25"/>
       <c r="B11" s="22"/>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="17" t="s">
         <v>45</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="13"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="34"/>
+      <c r="A12" s="25"/>
       <c r="B12" s="22"/>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="17" t="s">
         <v>46</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="13"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="34"/>
+      <c r="A13" s="25"/>
       <c r="B13" s="22"/>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="17" t="s">
         <v>24</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="13"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="34"/>
+      <c r="A14" s="25"/>
       <c r="B14" s="22"/>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="17" t="s">
         <v>25</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="13"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="34"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="21" t="s">
-        <v>26</v>
+      <c r="A15" s="25"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="17" t="s">
+        <v>113</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="13"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="34"/>
-      <c r="B16" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>27</v>
+      <c r="A16" s="25"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="13"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="34"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="27" t="s">
-        <v>28</v>
+      <c r="A17" s="25"/>
+      <c r="B17" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>27</v>
       </c>
       <c r="D17" s="12"/>
       <c r="E17" s="13"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="34"/>
-      <c r="B18" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>29</v>
+      <c r="A18" s="25"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="19" t="s">
+        <v>28</v>
       </c>
       <c r="D18" s="12"/>
       <c r="E18" s="13"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="34"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="21" t="s">
-        <v>30</v>
+      <c r="A19" s="25"/>
+      <c r="B19" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>29</v>
       </c>
       <c r="D19" s="12"/>
       <c r="E19" s="13"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="34"/>
+      <c r="A20" s="25"/>
       <c r="B20" s="22"/>
-      <c r="C20" s="21" t="s">
-        <v>31</v>
+      <c r="C20" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="D20" s="12"/>
       <c r="E20" s="13"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="34"/>
+      <c r="A21" s="25"/>
       <c r="B21" s="22"/>
-      <c r="C21" s="21" t="s">
-        <v>32</v>
+      <c r="C21" s="17" t="s">
+        <v>31</v>
       </c>
       <c r="D21" s="12"/>
       <c r="E21" s="13"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="34"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="21" t="s">
-        <v>33</v>
+      <c r="A22" s="25"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="17" t="s">
+        <v>32</v>
       </c>
       <c r="D22" s="12"/>
       <c r="E22" s="13"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="34"/>
-      <c r="B23" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>14</v>
+      <c r="A23" s="25"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="13"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="34"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="27" t="s">
-        <v>39</v>
+      <c r="A24" s="25"/>
+      <c r="B24" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>14</v>
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="13"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="34"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="27" t="s">
-        <v>15</v>
+      <c r="A25" s="25"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="19" t="s">
+        <v>39</v>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="13"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="34"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="27" t="s">
-        <v>41</v>
+      <c r="A26" s="25"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="13"/>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="34"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="27" t="s">
-        <v>40</v>
+      <c r="A27" s="25"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="19" t="s">
+        <v>41</v>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="13"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="34"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="27" t="s">
-        <v>43</v>
+      <c r="A28" s="25"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="19" t="s">
+        <v>40</v>
       </c>
       <c r="D28" s="12"/>
       <c r="E28" s="13"/>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="34"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="27" t="s">
-        <v>34</v>
+      <c r="A29" s="25"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="19" t="s">
+        <v>43</v>
       </c>
       <c r="D29" s="12"/>
       <c r="E29" s="13"/>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="34"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="27" t="s">
-        <v>35</v>
+      <c r="A30" s="25"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="19" t="s">
+        <v>34</v>
       </c>
       <c r="D30" s="12"/>
       <c r="E30" s="13"/>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="34"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="27" t="s">
-        <v>36</v>
+      <c r="A31" s="25"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="19" t="s">
+        <v>35</v>
       </c>
       <c r="D31" s="12"/>
       <c r="E31" s="13"/>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="34"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="27" t="s">
-        <v>37</v>
+      <c r="A32" s="25"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="19" t="s">
+        <v>36</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="13"/>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="34"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="27" t="s">
-        <v>38</v>
+      <c r="A33" s="25"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="19" t="s">
+        <v>37</v>
       </c>
       <c r="D33" s="12"/>
       <c r="E33" s="13"/>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="34"/>
-      <c r="B34" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>42</v>
+      <c r="A34" s="25"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="19" t="s">
+        <v>114</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="13"/>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="34"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="21" t="s">
-        <v>47</v>
+      <c r="A35" s="25"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="19" t="s">
+        <v>38</v>
       </c>
       <c r="D35" s="12"/>
       <c r="E35" s="13"/>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="34"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="21" t="s">
-        <v>48</v>
+      <c r="A36" s="25"/>
+      <c r="B36" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>42</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="13"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="34"/>
-      <c r="B37" s="23"/>
-      <c r="C37" s="21" t="s">
-        <v>80</v>
+      <c r="A37" s="25"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="17" t="s">
+        <v>47</v>
       </c>
       <c r="D37" s="12"/>
       <c r="E37" s="13"/>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="34"/>
-      <c r="B38" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="27" t="s">
-        <v>49</v>
+      <c r="A38" s="25"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="17" t="s">
+        <v>48</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="13"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="34"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="27" t="s">
-        <v>50</v>
+      <c r="A39" s="25"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="17" t="s">
+        <v>80</v>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="13"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="34"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="27" t="s">
-        <v>51</v>
+      <c r="A40" s="25"/>
+      <c r="B40" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>49</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="13"/>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="34"/>
-      <c r="B41" s="28"/>
-      <c r="C41" s="27" t="s">
-        <v>52</v>
+      <c r="A41" s="25"/>
+      <c r="B41" s="38"/>
+      <c r="C41" s="19" t="s">
+        <v>50</v>
       </c>
       <c r="D41" s="12"/>
       <c r="E41" s="13"/>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="34"/>
-      <c r="B42" s="28"/>
-      <c r="C42" s="27" t="s">
-        <v>53</v>
+      <c r="A42" s="25"/>
+      <c r="B42" s="38"/>
+      <c r="C42" s="19" t="s">
+        <v>51</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="13"/>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="34"/>
-      <c r="B43" s="28"/>
-      <c r="C43" s="27" t="s">
-        <v>54</v>
+      <c r="A43" s="25"/>
+      <c r="B43" s="38"/>
+      <c r="C43" s="19" t="s">
+        <v>52</v>
       </c>
       <c r="D43" s="12"/>
       <c r="E43" s="13"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="34"/>
-      <c r="B44" s="30"/>
-      <c r="C44" s="27" t="s">
-        <v>65</v>
+      <c r="A44" s="25"/>
+      <c r="B44" s="38"/>
+      <c r="C44" s="19" t="s">
+        <v>53</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="13"/>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="34"/>
-      <c r="B45" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C45" s="21" t="s">
-        <v>56</v>
+      <c r="A45" s="25"/>
+      <c r="B45" s="38"/>
+      <c r="C45" s="19" t="s">
+        <v>54</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="13"/>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="34"/>
-      <c r="B46" s="22"/>
-      <c r="C46" s="21" t="s">
-        <v>57</v>
+      <c r="A46" s="25"/>
+      <c r="B46" s="37"/>
+      <c r="C46" s="19" t="s">
+        <v>65</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="13"/>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="34"/>
-      <c r="B47" s="22"/>
-      <c r="C47" s="21" t="s">
-        <v>59</v>
+      <c r="A47" s="25"/>
+      <c r="B47" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>56</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="13"/>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="34"/>
+      <c r="A48" s="25"/>
       <c r="B48" s="22"/>
-      <c r="C48" s="21" t="s">
-        <v>60</v>
+      <c r="C48" s="17" t="s">
+        <v>57</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="13"/>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="34"/>
+      <c r="A49" s="25"/>
       <c r="B49" s="22"/>
-      <c r="C49" s="21" t="s">
-        <v>61</v>
+      <c r="C49" s="17" t="s">
+        <v>59</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="13"/>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="34"/>
+      <c r="A50" s="25"/>
       <c r="B50" s="22"/>
-      <c r="C50" s="21" t="s">
-        <v>62</v>
+      <c r="C50" s="17" t="s">
+        <v>60</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="13"/>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="34"/>
-      <c r="B51" s="23"/>
-      <c r="C51" s="21" t="s">
-        <v>64</v>
+      <c r="A51" s="25"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="17" t="s">
+        <v>61</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="13"/>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="34"/>
-      <c r="B52" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="C52" s="27" t="s">
-        <v>67</v>
+      <c r="A52" s="25"/>
+      <c r="B52" s="22"/>
+      <c r="C52" s="17" t="s">
+        <v>62</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="13"/>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="34"/>
-      <c r="B53" s="28"/>
-      <c r="C53" s="27" t="s">
-        <v>68</v>
+      <c r="A53" s="25"/>
+      <c r="B53" s="23"/>
+      <c r="C53" s="17" t="s">
+        <v>64</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="13"/>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="34"/>
-      <c r="B54" s="28"/>
-      <c r="C54" s="27" t="s">
-        <v>69</v>
+      <c r="A54" s="25"/>
+      <c r="B54" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>67</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="13"/>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="34"/>
-      <c r="B55" s="28"/>
-      <c r="C55" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="D55" s="12"/>
+      <c r="A55" s="25"/>
+      <c r="B55" s="38"/>
+      <c r="C55" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="E55" s="13"/>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="34"/>
-      <c r="B56" s="28"/>
-      <c r="C56" s="27" t="s">
-        <v>63</v>
+      <c r="A56" s="25"/>
+      <c r="B56" s="38"/>
+      <c r="C56" s="19" t="s">
+        <v>69</v>
       </c>
       <c r="D56" s="12"/>
       <c r="E56" s="13"/>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="34"/>
-      <c r="B57" s="28"/>
-      <c r="C57" s="27" t="s">
-        <v>71</v>
+      <c r="A57" s="25"/>
+      <c r="B57" s="38"/>
+      <c r="C57" s="19" t="s">
+        <v>70</v>
       </c>
       <c r="D57" s="12"/>
       <c r="E57" s="13"/>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="34"/>
-      <c r="B58" s="30"/>
-      <c r="C58" s="27" t="s">
-        <v>55</v>
+      <c r="A58" s="25"/>
+      <c r="B58" s="38"/>
+      <c r="C58" s="19" t="s">
+        <v>63</v>
       </c>
       <c r="D58" s="12"/>
       <c r="E58" s="13"/>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="34"/>
-      <c r="B59" s="20" t="s">
+      <c r="A59" s="25"/>
+      <c r="B59" s="38"/>
+      <c r="C59" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E59" s="13"/>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="25"/>
+      <c r="B60" s="37"/>
+      <c r="C60" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E60" s="13"/>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="25"/>
+      <c r="B61" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C59" s="21" t="s">
+      <c r="C61" s="17" t="s">
         <v>72</v>
-      </c>
-      <c r="D59" s="12"/>
-      <c r="E59" s="13"/>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="34"/>
-      <c r="B60" s="22"/>
-      <c r="C60" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="D60" s="12"/>
-      <c r="E60" s="13"/>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="34"/>
-      <c r="B61" s="22"/>
-      <c r="C61" s="21" t="s">
-        <v>74</v>
       </c>
       <c r="D61" s="12"/>
       <c r="E61" s="13"/>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="34"/>
+      <c r="A62" s="25"/>
       <c r="B62" s="22"/>
-      <c r="C62" s="21" t="s">
-        <v>75</v>
+      <c r="C62" s="17" t="s">
+        <v>73</v>
       </c>
       <c r="D62" s="12"/>
       <c r="E62" s="13"/>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="34"/>
+      <c r="A63" s="25"/>
       <c r="B63" s="22"/>
-      <c r="C63" s="21" t="s">
-        <v>76</v>
+      <c r="C63" s="17" t="s">
+        <v>74</v>
       </c>
       <c r="D63" s="12"/>
       <c r="E63" s="13"/>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="34"/>
+      <c r="A64" s="25"/>
       <c r="B64" s="22"/>
-      <c r="C64" s="21" t="s">
-        <v>78</v>
+      <c r="C64" s="17" t="s">
+        <v>75</v>
       </c>
       <c r="D64" s="12"/>
       <c r="E64" s="13"/>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="34"/>
+      <c r="A65" s="25"/>
       <c r="B65" s="22"/>
-      <c r="C65" s="21" t="s">
-        <v>77</v>
+      <c r="C65" s="17" t="s">
+        <v>76</v>
       </c>
       <c r="D65" s="12"/>
       <c r="E65" s="13"/>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="34"/>
+      <c r="A66" s="25"/>
       <c r="B66" s="22"/>
-      <c r="C66" s="21" t="s">
-        <v>84</v>
+      <c r="C66" s="17" t="s">
+        <v>78</v>
       </c>
       <c r="D66" s="12"/>
       <c r="E66" s="13"/>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="34"/>
+      <c r="A67" s="25"/>
       <c r="B67" s="22"/>
-      <c r="C67" s="21" t="s">
-        <v>85</v>
+      <c r="C67" s="17" t="s">
+        <v>77</v>
       </c>
       <c r="D67" s="12"/>
       <c r="E67" s="13"/>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="34"/>
-      <c r="B68" s="23"/>
-      <c r="C68" s="21" t="s">
-        <v>79</v>
+      <c r="A68" s="25"/>
+      <c r="B68" s="22"/>
+      <c r="C68" s="17" t="s">
+        <v>83</v>
       </c>
       <c r="D68" s="12"/>
       <c r="E68" s="13"/>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="34"/>
-      <c r="B69" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="C69" s="27"/>
+      <c r="A69" s="25"/>
+      <c r="B69" s="22"/>
+      <c r="C69" s="17" t="s">
+        <v>84</v>
+      </c>
       <c r="D69" s="12"/>
       <c r="E69" s="13"/>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="34"/>
-      <c r="B70" s="30"/>
-      <c r="C70" s="27"/>
-      <c r="D70" s="12"/>
+      <c r="A70" s="25"/>
+      <c r="B70" s="22"/>
+      <c r="C70" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="E70" s="13"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="31"/>
-      <c r="B71" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="C71" s="21" t="s">
-        <v>89</v>
+      <c r="A71" s="25"/>
+      <c r="B71" s="23"/>
+      <c r="C71" s="17" t="s">
+        <v>79</v>
       </c>
       <c r="D71" s="12"/>
       <c r="E71" s="13"/>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="31"/>
-      <c r="B72" s="22"/>
-      <c r="C72" s="21"/>
+      <c r="A72" s="25"/>
+      <c r="B72" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="C72" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="D72" s="12"/>
       <c r="E72" s="13"/>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="31"/>
-      <c r="B73" s="22"/>
-      <c r="C73" s="21"/>
+      <c r="A73" s="25"/>
+      <c r="B73" s="38"/>
+      <c r="C73" s="19" t="s">
+        <v>100</v>
+      </c>
       <c r="D73" s="12"/>
       <c r="E73" s="13"/>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="31"/>
-      <c r="B74" s="22"/>
-      <c r="C74" s="21"/>
+      <c r="A74" s="25"/>
+      <c r="B74" s="37"/>
+      <c r="C74" s="19" t="s">
+        <v>99</v>
+      </c>
       <c r="D74" s="12"/>
       <c r="E74" s="13"/>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="32"/>
-      <c r="B75" s="23"/>
-      <c r="C75" s="21"/>
-      <c r="D75" s="12"/>
+      <c r="A75" s="26"/>
+      <c r="B75" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C75" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="E75" s="13"/>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="B76" s="17"/>
-      <c r="C76" s="11" t="s">
-        <v>91</v>
-      </c>
+      <c r="A76" s="26"/>
+      <c r="B76" s="22"/>
+      <c r="C76" s="17"/>
       <c r="D76" s="12"/>
       <c r="E76" s="13"/>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="37"/>
-      <c r="B77" s="18"/>
-      <c r="C77" s="11" t="s">
-        <v>83</v>
-      </c>
+      <c r="A77" s="26"/>
+      <c r="B77" s="22"/>
+      <c r="C77" s="17"/>
       <c r="D77" s="12"/>
       <c r="E77" s="13"/>
     </row>
     <row r="78" spans="1:5">
-      <c r="A78" s="37"/>
-      <c r="B78" s="18"/>
-      <c r="C78" s="11" t="s">
-        <v>87</v>
-      </c>
+      <c r="A78" s="26"/>
+      <c r="B78" s="22"/>
+      <c r="C78" s="17"/>
       <c r="D78" s="12"/>
       <c r="E78" s="13"/>
     </row>
     <row r="79" spans="1:5">
-      <c r="A79" s="37"/>
-      <c r="B79" s="18"/>
-      <c r="C79" s="11" t="s">
-        <v>90</v>
-      </c>
+      <c r="A79" s="27"/>
+      <c r="B79" s="23"/>
+      <c r="C79" s="17"/>
       <c r="D79" s="12"/>
       <c r="E79" s="13"/>
     </row>
     <row r="80" spans="1:5">
-      <c r="A80" s="38"/>
-      <c r="B80" s="19"/>
-      <c r="C80" s="11"/>
+      <c r="A80" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80" s="31"/>
+      <c r="C80" s="11" t="s">
+        <v>90</v>
+      </c>
       <c r="D80" s="12"/>
       <c r="E80" s="13"/>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C81" s="11"/>
+      <c r="A81" s="29"/>
+      <c r="B81" s="32"/>
+      <c r="C81" s="11" t="s">
+        <v>115</v>
+      </c>
       <c r="D81" s="12"/>
       <c r="E81" s="13"/>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="34"/>
-      <c r="B82" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C82" s="11"/>
+      <c r="A82" s="29"/>
+      <c r="B82" s="32"/>
+      <c r="C82" s="11" t="s">
+        <v>86</v>
+      </c>
       <c r="D82" s="12"/>
       <c r="E82" s="13"/>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="34"/>
-      <c r="B83" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C83" s="11"/>
+      <c r="A83" s="29"/>
+      <c r="B83" s="32"/>
+      <c r="C83" s="11" t="s">
+        <v>89</v>
+      </c>
       <c r="D83" s="12"/>
       <c r="E83" s="13"/>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="34"/>
-      <c r="B84" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C84" s="11"/>
+      <c r="A84" s="30"/>
+      <c r="B84" s="33"/>
+      <c r="C84" s="11" t="s">
+        <v>101</v>
+      </c>
       <c r="D84" s="12"/>
       <c r="E84" s="13"/>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="35"/>
-      <c r="B85" s="6"/>
-      <c r="C85" s="11"/>
-      <c r="D85" s="12"/>
+      <c r="A85" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C85" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="E85" s="13"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="5"/>
-      <c r="B86" s="6"/>
-      <c r="C86" s="11"/>
-      <c r="D86" s="12"/>
+      <c r="A86" s="25"/>
+      <c r="B86" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C86" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="E86" s="13"/>
     </row>
-    <row r="87" spans="1:5" ht="14.25" thickBot="1">
-      <c r="A87" s="7"/>
-      <c r="B87" s="8"/>
-      <c r="C87" s="14"/>
-      <c r="D87" s="15"/>
-      <c r="E87" s="16"/>
+    <row r="87" spans="1:5">
+      <c r="A87" s="25"/>
+      <c r="B87" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E87" s="13"/>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="25"/>
+      <c r="B88" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C88" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E88" s="13"/>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="25"/>
+      <c r="B89" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E89" s="13"/>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="25"/>
+      <c r="B90" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C90" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E90" s="13"/>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="35"/>
+      <c r="B91" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C91" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E91" s="13"/>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="5"/>
+      <c r="B92" s="6"/>
+      <c r="C92" s="11"/>
+      <c r="D92" s="12"/>
+      <c r="E92" s="13"/>
+    </row>
+    <row r="93" spans="1:5" ht="14.25" thickBot="1">
+      <c r="A93" s="7"/>
+      <c r="B93" s="8"/>
+      <c r="C93" s="14"/>
+      <c r="D93" s="15"/>
+      <c r="E93" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B71:B75"/>
-    <mergeCell ref="A2:A75"/>
-    <mergeCell ref="A76:A80"/>
-    <mergeCell ref="B76:B80"/>
-    <mergeCell ref="A81:A85"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="B45:B51"/>
-    <mergeCell ref="B52:B58"/>
-    <mergeCell ref="B59:B68"/>
+    <mergeCell ref="B24:B35"/>
+    <mergeCell ref="B75:B79"/>
+    <mergeCell ref="A2:A79"/>
+    <mergeCell ref="A80:A84"/>
+    <mergeCell ref="B80:B84"/>
+    <mergeCell ref="A85:A91"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B36:B39"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="B47:B53"/>
+    <mergeCell ref="B54:B60"/>
+    <mergeCell ref="B61:B71"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B18:B22"/>
-    <mergeCell ref="B23:B33"/>
+    <mergeCell ref="B10:B16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B19:B23"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/01.需求特性/版本特性列表.xlsx
+++ b/internal_doc/01.需求特性/版本特性列表.xlsx
@@ -11,12 +11,15 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">版本特性表!$A$2:$E$92</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="121">
   <si>
     <t>内容项</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -402,14 +405,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>#</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>白皮书</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -479,6 +474,34 @@
   </si>
   <si>
     <t>与spark（spark sql\spark stream）集成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>√</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>■</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>□</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>√</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>×</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>□</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>√已实现   □已规划   ×不支持   ■条件支持</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -486,7 +509,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -502,8 +525,17 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -540,8 +572,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3FFF96"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="23">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -847,13 +885,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -881,30 +956,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -917,6 +974,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -962,17 +1025,38 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -980,6 +1064,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF3FFF96"/>
+    </mruColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1271,946 +1360,1268 @@
   <sheetPr codeName="Sheet1">
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.5" customWidth="1"/>
     <col min="2" max="2" width="15.375" customWidth="1"/>
     <col min="3" max="3" width="40.125" customWidth="1"/>
-    <col min="4" max="4" width="21.125" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="4" max="5" width="18.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" thickBot="1">
+      <c r="A1" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="42"/>
+    </row>
+    <row r="2" spans="1:5" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="14.25" thickTop="1">
-      <c r="A2" s="24" t="s">
+    <row r="3" spans="1:5" ht="14.25" thickTop="1">
+      <c r="A3" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B3" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="10"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="25"/>
-      <c r="B3" s="22"/>
-      <c r="C3" s="18" t="s">
+      <c r="D3" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="21"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="13"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="25"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="17" t="s">
+      <c r="D4" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="21"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="13"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="25"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="17" t="s">
+      <c r="D5" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="21"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="13"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="25"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="17" t="s">
+      <c r="D6" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="21"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D7" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="21"/>
+      <c r="B8" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" s="36" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="21"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" s="36" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="21"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E10" s="36" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="21"/>
+      <c r="B11" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="21"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="21"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E13" s="36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="21"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E14" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="21"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="21"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E16" s="36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="21"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E17" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="21"/>
+      <c r="B18" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E18" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="21"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E19" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="21"/>
+      <c r="B20" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="21"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E21" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="21"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="21"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="21"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="21"/>
+      <c r="B25" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="21"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="21"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="21"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D28" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E28" s="36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="21"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="21"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="21"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="21"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="21"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="21"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E34" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="21"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D35" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E35" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="21"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E36" s="36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="21"/>
+      <c r="B37" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E37" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="21"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D38" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E38" s="36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="21"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D39" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E39" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="21"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E40" s="36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="21"/>
+      <c r="B41" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D41" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E41" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="21"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D42" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E42" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="21"/>
+      <c r="B43" s="16"/>
+      <c r="C43" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D43" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E43" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="21"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E44" s="36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="21"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D45" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E45" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="21"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D46" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E46" s="36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="21"/>
+      <c r="B47" s="32"/>
+      <c r="C47" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D47" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E47" s="36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="21"/>
+      <c r="B48" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D48" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E48" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="21"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D49" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E49" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="21"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D50" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E50" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="21"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D51" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E51" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="21"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D52" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E52" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="21"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D53" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E53" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="21"/>
+      <c r="B54" s="19"/>
+      <c r="C54" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D54" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E54" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="21"/>
+      <c r="B55" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D55" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E55" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="21"/>
+      <c r="B56" s="16"/>
+      <c r="C56" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D56" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E56" s="36" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="21"/>
+      <c r="B57" s="16"/>
+      <c r="C57" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D57" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E57" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="21"/>
+      <c r="B58" s="16"/>
+      <c r="C58" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D58" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E58" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="21"/>
+      <c r="B59" s="16"/>
+      <c r="C59" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D59" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E59" s="36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="21"/>
+      <c r="B60" s="16"/>
+      <c r="C60" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D60" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E60" s="36" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="21"/>
+      <c r="B61" s="32"/>
+      <c r="C61" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D61" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E61" s="36" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="21"/>
+      <c r="B62" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D62" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E62" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="21"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D63" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E63" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="21"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D64" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E64" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="21"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D65" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E65" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="21"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D66" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E66" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="21"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D67" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E67" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="21"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D68" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E68" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="21"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D69" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E69" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="21"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D70" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E70" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="21"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="D71" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E71" s="36" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="21"/>
+      <c r="B72" s="19"/>
+      <c r="C72" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D72" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E72" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="21"/>
+      <c r="B73" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C73" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="E6" s="13"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="25"/>
-      <c r="B7" s="36" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="12" t="s">
+      <c r="D73" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E73" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="21"/>
+      <c r="B74" s="16"/>
+      <c r="C74" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D74" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E74" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="21"/>
+      <c r="B75" s="32"/>
+      <c r="C75" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="E7" s="13"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="25"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E8" s="13"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="25"/>
-      <c r="B9" s="37"/>
-      <c r="C9" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E9" s="13"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="25"/>
-      <c r="B10" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="13"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="25"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="13"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="25"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="13"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="25"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="13"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="25"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="13"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="25"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="17" t="s">
+      <c r="D75" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E75" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="22"/>
+      <c r="B76" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D76" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E76" s="36" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="22"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="11"/>
+      <c r="D77" s="34"/>
+      <c r="E77" s="36"/>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="22"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="11"/>
+      <c r="D78" s="34"/>
+      <c r="E78" s="36"/>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="22"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="34"/>
+      <c r="E79" s="36"/>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="23"/>
+      <c r="B80" s="19"/>
+      <c r="C80" s="11"/>
+      <c r="D80" s="34"/>
+      <c r="E80" s="36"/>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="B81" s="27"/>
+      <c r="C81" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D81" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E81" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="25"/>
+      <c r="B82" s="28"/>
+      <c r="C82" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D15" s="12"/>
-      <c r="E15" s="13"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="25"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="12"/>
-      <c r="E16" s="13"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="25"/>
-      <c r="B17" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="13"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="25"/>
-      <c r="B18" s="37"/>
-      <c r="C18" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="13"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="25"/>
-      <c r="B19" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="12"/>
-      <c r="E19" s="13"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="25"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="13"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="25"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="12"/>
-      <c r="E21" s="13"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="25"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" s="12"/>
-      <c r="E22" s="13"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="25"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23" s="12"/>
-      <c r="E23" s="13"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="25"/>
-      <c r="B24" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" s="12"/>
-      <c r="E24" s="13"/>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="25"/>
-      <c r="B25" s="38"/>
-      <c r="C25" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="12"/>
-      <c r="E25" s="13"/>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="25"/>
-      <c r="B26" s="38"/>
-      <c r="C26" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" s="12"/>
-      <c r="E26" s="13"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="25"/>
-      <c r="B27" s="38"/>
-      <c r="C27" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="12"/>
-      <c r="E27" s="13"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="25"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="D28" s="12"/>
-      <c r="E28" s="13"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="25"/>
-      <c r="B29" s="38"/>
-      <c r="C29" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" s="12"/>
-      <c r="E29" s="13"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="25"/>
-      <c r="B30" s="38"/>
-      <c r="C30" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" s="12"/>
-      <c r="E30" s="13"/>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="25"/>
-      <c r="B31" s="38"/>
-      <c r="C31" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D31" s="12"/>
-      <c r="E31" s="13"/>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="25"/>
-      <c r="B32" s="38"/>
-      <c r="C32" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="D32" s="12"/>
-      <c r="E32" s="13"/>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="25"/>
-      <c r="B33" s="38"/>
-      <c r="C33" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D33" s="12"/>
-      <c r="E33" s="13"/>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="25"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D34" s="12"/>
-      <c r="E34" s="13"/>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="25"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="D35" s="12"/>
-      <c r="E35" s="13"/>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="25"/>
-      <c r="B36" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" s="12"/>
-      <c r="E36" s="13"/>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="25"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D37" s="12"/>
-      <c r="E37" s="13"/>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="25"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D38" s="12"/>
-      <c r="E38" s="13"/>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="25"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="D39" s="12"/>
-      <c r="E39" s="13"/>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="25"/>
-      <c r="B40" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="D40" s="12"/>
-      <c r="E40" s="13"/>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="25"/>
-      <c r="B41" s="38"/>
-      <c r="C41" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="D41" s="12"/>
-      <c r="E41" s="13"/>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="25"/>
-      <c r="B42" s="38"/>
-      <c r="C42" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D42" s="12"/>
-      <c r="E42" s="13"/>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="25"/>
-      <c r="B43" s="38"/>
-      <c r="C43" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D43" s="12"/>
-      <c r="E43" s="13"/>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="25"/>
-      <c r="B44" s="38"/>
-      <c r="C44" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D44" s="12"/>
-      <c r="E44" s="13"/>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="25"/>
-      <c r="B45" s="38"/>
-      <c r="C45" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D45" s="12"/>
-      <c r="E45" s="13"/>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="25"/>
-      <c r="B46" s="37"/>
-      <c r="C46" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="D46" s="12"/>
-      <c r="E46" s="13"/>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="25"/>
-      <c r="B47" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C47" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D47" s="12"/>
-      <c r="E47" s="13"/>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="25"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="D48" s="12"/>
-      <c r="E48" s="13"/>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="25"/>
-      <c r="B49" s="22"/>
-      <c r="C49" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="D49" s="12"/>
-      <c r="E49" s="13"/>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="25"/>
-      <c r="B50" s="22"/>
-      <c r="C50" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="D50" s="12"/>
-      <c r="E50" s="13"/>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="25"/>
-      <c r="B51" s="22"/>
-      <c r="C51" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D51" s="12"/>
-      <c r="E51" s="13"/>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="25"/>
-      <c r="B52" s="22"/>
-      <c r="C52" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D52" s="12"/>
-      <c r="E52" s="13"/>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="25"/>
-      <c r="B53" s="23"/>
-      <c r="C53" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="D53" s="12"/>
-      <c r="E53" s="13"/>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="25"/>
-      <c r="B54" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="C54" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="D54" s="12"/>
-      <c r="E54" s="13"/>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="25"/>
-      <c r="B55" s="38"/>
-      <c r="C55" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E55" s="13"/>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="25"/>
-      <c r="B56" s="38"/>
-      <c r="C56" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="D56" s="12"/>
-      <c r="E56" s="13"/>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="25"/>
-      <c r="B57" s="38"/>
-      <c r="C57" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="D57" s="12"/>
-      <c r="E57" s="13"/>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="25"/>
-      <c r="B58" s="38"/>
-      <c r="C58" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="D58" s="12"/>
-      <c r="E58" s="13"/>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="25"/>
-      <c r="B59" s="38"/>
-      <c r="C59" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E59" s="13"/>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="25"/>
-      <c r="B60" s="37"/>
-      <c r="C60" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E60" s="13"/>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="25"/>
-      <c r="B61" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C61" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D61" s="12"/>
-      <c r="E61" s="13"/>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="25"/>
-      <c r="B62" s="22"/>
-      <c r="C62" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D62" s="12"/>
-      <c r="E62" s="13"/>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="25"/>
-      <c r="B63" s="22"/>
-      <c r="C63" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="D63" s="12"/>
-      <c r="E63" s="13"/>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="25"/>
-      <c r="B64" s="22"/>
-      <c r="C64" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D64" s="12"/>
-      <c r="E64" s="13"/>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="25"/>
-      <c r="B65" s="22"/>
-      <c r="C65" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D65" s="12"/>
-      <c r="E65" s="13"/>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="25"/>
-      <c r="B66" s="22"/>
-      <c r="C66" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="D66" s="12"/>
-      <c r="E66" s="13"/>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="25"/>
-      <c r="B67" s="22"/>
-      <c r="C67" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D67" s="12"/>
-      <c r="E67" s="13"/>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="25"/>
-      <c r="B68" s="22"/>
-      <c r="C68" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="D68" s="12"/>
-      <c r="E68" s="13"/>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="25"/>
-      <c r="B69" s="22"/>
-      <c r="C69" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="D69" s="12"/>
-      <c r="E69" s="13"/>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="25"/>
-      <c r="B70" s="22"/>
-      <c r="C70" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="D70" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E70" s="13"/>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="25"/>
-      <c r="B71" s="23"/>
-      <c r="C71" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D71" s="12"/>
-      <c r="E71" s="13"/>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="25"/>
-      <c r="B72" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="C72" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="D72" s="12"/>
-      <c r="E72" s="13"/>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="25"/>
-      <c r="B73" s="38"/>
-      <c r="C73" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="D73" s="12"/>
-      <c r="E73" s="13"/>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="25"/>
-      <c r="B74" s="37"/>
-      <c r="C74" s="19" t="s">
+      <c r="D82" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E82" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="25"/>
+      <c r="B83" s="28"/>
+      <c r="C83" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D83" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E83" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="25"/>
+      <c r="B84" s="28"/>
+      <c r="C84" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D84" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E84" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="26"/>
+      <c r="B85" s="29"/>
+      <c r="C85" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="D74" s="12"/>
-      <c r="E74" s="13"/>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="26"/>
-      <c r="B75" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C75" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D75" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E75" s="13"/>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="26"/>
-      <c r="B76" s="22"/>
-      <c r="C76" s="17"/>
-      <c r="D76" s="12"/>
-      <c r="E76" s="13"/>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="26"/>
-      <c r="B77" s="22"/>
-      <c r="C77" s="17"/>
-      <c r="D77" s="12"/>
-      <c r="E77" s="13"/>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="26"/>
-      <c r="B78" s="22"/>
-      <c r="C78" s="17"/>
-      <c r="D78" s="12"/>
-      <c r="E78" s="13"/>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="27"/>
-      <c r="B79" s="23"/>
-      <c r="C79" s="17"/>
-      <c r="D79" s="12"/>
-      <c r="E79" s="13"/>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="B80" s="31"/>
-      <c r="C80" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D80" s="12"/>
-      <c r="E80" s="13"/>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="29"/>
-      <c r="B81" s="32"/>
-      <c r="C81" s="11" t="s">
+      <c r="D85" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E85" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D86" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="E86" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="D81" s="12"/>
-      <c r="E81" s="13"/>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="29"/>
-      <c r="B82" s="32"/>
-      <c r="C82" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D82" s="12"/>
-      <c r="E82" s="13"/>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="29"/>
-      <c r="B83" s="32"/>
-      <c r="C83" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D83" s="12"/>
-      <c r="E83" s="13"/>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="30"/>
-      <c r="B84" s="33"/>
-      <c r="C84" s="11" t="s">
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="21"/>
+      <c r="B87" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D87" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="E87" s="36" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="21"/>
+      <c r="B88" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D88" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="E88" s="36" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="21"/>
+      <c r="B89" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D89" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="E89" s="36" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="21"/>
+      <c r="B90" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D84" s="12"/>
-      <c r="E84" s="13"/>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C85" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D85" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E85" s="13"/>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="25"/>
-      <c r="B86" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C86" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D86" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E86" s="13"/>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="25"/>
-      <c r="B87" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C87" s="11" t="s">
+      <c r="C90" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="D87" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E87" s="13"/>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="25"/>
-      <c r="B88" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C88" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="D88" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E88" s="13"/>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" s="25"/>
-      <c r="B89" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C89" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="D89" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E89" s="13"/>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="25"/>
-      <c r="B90" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C90" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D90" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E90" s="13"/>
+      <c r="D90" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="E90" s="36" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="35"/>
+      <c r="A91" s="21"/>
       <c r="B91" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C91" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D91" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E91" s="13"/>
+      <c r="C91" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D91" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="E91" s="36" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="5"/>
-      <c r="B92" s="6"/>
-      <c r="C92" s="11"/>
-      <c r="D92" s="12"/>
-      <c r="E92" s="13"/>
-    </row>
-    <row r="93" spans="1:5" ht="14.25" thickBot="1">
-      <c r="A93" s="7"/>
-      <c r="B93" s="8"/>
-      <c r="C93" s="14"/>
-      <c r="D93" s="15"/>
-      <c r="E93" s="16"/>
+      <c r="A92" s="31"/>
+      <c r="B92" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D92" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="E92" s="36" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="5"/>
+      <c r="B93" s="6"/>
+      <c r="C93" s="9"/>
+      <c r="D93" s="34"/>
+      <c r="E93" s="36"/>
+    </row>
+    <row r="94" spans="1:5" ht="14.25" thickBot="1">
+      <c r="A94" s="7"/>
+      <c r="B94" s="8"/>
+      <c r="C94" s="10"/>
+      <c r="D94" s="37"/>
+      <c r="E94" s="38"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="B24:B35"/>
-    <mergeCell ref="B75:B79"/>
-    <mergeCell ref="A2:A79"/>
-    <mergeCell ref="A80:A84"/>
-    <mergeCell ref="B80:B84"/>
-    <mergeCell ref="A85:A91"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="B36:B39"/>
-    <mergeCell ref="B40:B46"/>
-    <mergeCell ref="B47:B53"/>
-    <mergeCell ref="B54:B60"/>
-    <mergeCell ref="B61:B71"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B19:B23"/>
+  <autoFilter ref="A2:E92"/>
+  <mergeCells count="18">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A86:A92"/>
+    <mergeCell ref="B73:B75"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="B41:B47"/>
+    <mergeCell ref="B48:B54"/>
+    <mergeCell ref="B55:B61"/>
+    <mergeCell ref="B62:B72"/>
+    <mergeCell ref="B25:B36"/>
+    <mergeCell ref="B76:B80"/>
+    <mergeCell ref="A3:A80"/>
+    <mergeCell ref="A81:A85"/>
+    <mergeCell ref="B81:B85"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B20:B24"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/01.需求特性/版本特性列表.xlsx
+++ b/internal_doc/01.需求特性/版本特性列表.xlsx
@@ -461,10 +461,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SMTP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>数据库前滚+日志归档</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -502,6 +498,10 @@
   </si>
   <si>
     <t>√已实现   □已规划   ×不支持   ■条件支持</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SNMP</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -974,63 +974,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1057,6 +1000,63 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1370,13 +1370,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A1" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="42"/>
+      <c r="A1" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="23"/>
     </row>
     <row r="2" spans="1:5" ht="26.25" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="s">
@@ -1396,1092 +1396,1092 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="14.25" thickTop="1">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="42" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E3" s="35" t="s">
-        <v>114</v>
+      <c r="D3" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="21"/>
-      <c r="B4" s="18"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="31"/>
       <c r="C4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E4" s="36" t="s">
-        <v>116</v>
+      <c r="D4" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="21"/>
-      <c r="B5" s="18"/>
+      <c r="A5" s="25"/>
+      <c r="B5" s="31"/>
       <c r="C5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E5" s="36" t="s">
-        <v>116</v>
+      <c r="D5" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="21"/>
-      <c r="B6" s="18"/>
+      <c r="A6" s="25"/>
+      <c r="B6" s="31"/>
       <c r="C6" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E6" s="36" t="s">
-        <v>116</v>
+      <c r="D6" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="21"/>
-      <c r="B7" s="19"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="32"/>
       <c r="C7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="E7" s="36" t="s">
-        <v>118</v>
-      </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="21"/>
-      <c r="B8" s="15" t="s">
+      <c r="A8" s="25"/>
+      <c r="B8" s="27" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="E8" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="E8" s="36" t="s">
-        <v>118</v>
-      </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="21"/>
-      <c r="B9" s="16"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="28"/>
       <c r="C9" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="E9" s="36" t="s">
+      <c r="D9" s="20" t="s">
         <v>118</v>
       </c>
+      <c r="E9" s="17" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="21"/>
-      <c r="B10" s="32"/>
+      <c r="A10" s="25"/>
+      <c r="B10" s="29"/>
       <c r="C10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="E10" s="36" t="s">
+      <c r="D10" s="20" t="s">
         <v>118</v>
       </c>
+      <c r="E10" s="17" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="21"/>
-      <c r="B11" s="17" t="s">
+      <c r="A11" s="25"/>
+      <c r="B11" s="30" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="D11" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E11" s="36" t="s">
-        <v>114</v>
+      <c r="D11" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="21"/>
-      <c r="B12" s="18"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="31"/>
       <c r="C12" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E12" s="36" t="s">
-        <v>114</v>
+      <c r="D12" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="21"/>
-      <c r="B13" s="18"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="31"/>
       <c r="C13" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E13" s="36" t="s">
-        <v>116</v>
+      <c r="D13" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="21"/>
-      <c r="B14" s="18"/>
+      <c r="A14" s="25"/>
+      <c r="B14" s="31"/>
       <c r="C14" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E14" s="36" t="s">
-        <v>114</v>
+      <c r="D14" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="21"/>
-      <c r="B15" s="18"/>
+      <c r="A15" s="25"/>
+      <c r="B15" s="31"/>
       <c r="C15" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" s="36" t="s">
-        <v>114</v>
+      <c r="D15" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="21"/>
-      <c r="B16" s="18"/>
+      <c r="A16" s="25"/>
+      <c r="B16" s="31"/>
       <c r="C16" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D16" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E16" s="36" t="s">
-        <v>116</v>
+        <v>110</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="21"/>
-      <c r="B17" s="19"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="32"/>
       <c r="C17" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E17" s="36" t="s">
-        <v>114</v>
+      <c r="D17" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="21"/>
-      <c r="B18" s="15" t="s">
+      <c r="A18" s="25"/>
+      <c r="B18" s="27" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E18" s="36" t="s">
-        <v>114</v>
+      <c r="D18" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="21"/>
-      <c r="B19" s="32"/>
+      <c r="A19" s="25"/>
+      <c r="B19" s="29"/>
       <c r="C19" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E19" s="36" t="s">
-        <v>114</v>
+      <c r="D19" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="21"/>
-      <c r="B20" s="17" t="s">
+      <c r="A20" s="25"/>
+      <c r="B20" s="30" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>114</v>
+      <c r="D20" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="21"/>
-      <c r="B21" s="18"/>
+      <c r="A21" s="25"/>
+      <c r="B21" s="31"/>
       <c r="C21" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E21" s="36" t="s">
-        <v>114</v>
+      <c r="D21" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="21"/>
-      <c r="B22" s="18"/>
+      <c r="A22" s="25"/>
+      <c r="B22" s="31"/>
       <c r="C22" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E22" s="36" t="s">
-        <v>114</v>
+      <c r="D22" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="21"/>
-      <c r="B23" s="18"/>
+      <c r="A23" s="25"/>
+      <c r="B23" s="31"/>
       <c r="C23" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E23" s="36" t="s">
-        <v>114</v>
+      <c r="D23" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="21"/>
-      <c r="B24" s="19"/>
+      <c r="A24" s="25"/>
+      <c r="B24" s="32"/>
       <c r="C24" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="36" t="s">
-        <v>114</v>
+      <c r="D24" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="21"/>
-      <c r="B25" s="15" t="s">
+      <c r="A25" s="25"/>
+      <c r="B25" s="27" t="s">
         <v>13</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E25" s="36" t="s">
-        <v>114</v>
+      <c r="D25" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="21"/>
-      <c r="B26" s="16"/>
+      <c r="A26" s="25"/>
+      <c r="B26" s="28"/>
       <c r="C26" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D26" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E26" s="36" t="s">
-        <v>116</v>
+      <c r="D26" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="21"/>
-      <c r="B27" s="16"/>
+      <c r="A27" s="25"/>
+      <c r="B27" s="28"/>
       <c r="C27" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E27" s="36" t="s">
-        <v>114</v>
+      <c r="D27" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="21"/>
-      <c r="B28" s="16"/>
+      <c r="A28" s="25"/>
+      <c r="B28" s="28"/>
       <c r="C28" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D28" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E28" s="36" t="s">
-        <v>116</v>
+      <c r="D28" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="21"/>
-      <c r="B29" s="16"/>
+      <c r="A29" s="25"/>
+      <c r="B29" s="28"/>
       <c r="C29" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E29" s="36" t="s">
-        <v>116</v>
+      <c r="D29" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="21"/>
-      <c r="B30" s="16"/>
+      <c r="A30" s="25"/>
+      <c r="B30" s="28"/>
       <c r="C30" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D30" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E30" s="36" t="s">
-        <v>116</v>
+      <c r="D30" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="21"/>
-      <c r="B31" s="16"/>
+      <c r="A31" s="25"/>
+      <c r="B31" s="28"/>
       <c r="C31" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D31" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E31" s="36" t="s">
-        <v>114</v>
+      <c r="D31" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="21"/>
-      <c r="B32" s="16"/>
+      <c r="A32" s="25"/>
+      <c r="B32" s="28"/>
       <c r="C32" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E32" s="36" t="s">
-        <v>114</v>
+      <c r="D32" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="21"/>
-      <c r="B33" s="16"/>
+      <c r="A33" s="25"/>
+      <c r="B33" s="28"/>
       <c r="C33" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D33" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E33" s="36" t="s">
-        <v>114</v>
+      <c r="D33" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="21"/>
-      <c r="B34" s="16"/>
+      <c r="A34" s="25"/>
+      <c r="B34" s="28"/>
       <c r="C34" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D34" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E34" s="36" t="s">
-        <v>114</v>
+      <c r="D34" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="21"/>
-      <c r="B35" s="16"/>
+      <c r="A35" s="25"/>
+      <c r="B35" s="28"/>
       <c r="C35" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D35" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E35" s="36" t="s">
-        <v>114</v>
+        <v>111</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="21"/>
-      <c r="B36" s="16"/>
+      <c r="A36" s="25"/>
+      <c r="B36" s="28"/>
       <c r="C36" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E36" s="36" t="s">
-        <v>116</v>
+      <c r="D36" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="21"/>
-      <c r="B37" s="17" t="s">
+      <c r="A37" s="25"/>
+      <c r="B37" s="30" t="s">
         <v>44</v>
       </c>
       <c r="C37" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D37" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E37" s="36" t="s">
-        <v>114</v>
+      <c r="D37" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="21"/>
-      <c r="B38" s="18"/>
+      <c r="A38" s="25"/>
+      <c r="B38" s="31"/>
       <c r="C38" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D38" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E38" s="36" t="s">
-        <v>116</v>
+      <c r="D38" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="21"/>
-      <c r="B39" s="18"/>
+      <c r="A39" s="25"/>
+      <c r="B39" s="31"/>
       <c r="C39" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="D39" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E39" s="36" t="s">
-        <v>114</v>
+      <c r="D39" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="21"/>
-      <c r="B40" s="19"/>
+      <c r="A40" s="25"/>
+      <c r="B40" s="32"/>
       <c r="C40" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="D40" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E40" s="36" t="s">
-        <v>116</v>
+      <c r="D40" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="21"/>
-      <c r="B41" s="15" t="s">
+      <c r="A41" s="25"/>
+      <c r="B41" s="27" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E41" s="36" t="s">
-        <v>114</v>
+      <c r="D41" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="21"/>
-      <c r="B42" s="16"/>
+      <c r="A42" s="25"/>
+      <c r="B42" s="28"/>
       <c r="C42" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E42" s="36" t="s">
-        <v>114</v>
+      <c r="D42" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="21"/>
-      <c r="B43" s="16"/>
+      <c r="A43" s="25"/>
+      <c r="B43" s="28"/>
       <c r="C43" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E43" s="36" t="s">
-        <v>114</v>
+      <c r="D43" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="21"/>
-      <c r="B44" s="16"/>
+      <c r="A44" s="25"/>
+      <c r="B44" s="28"/>
       <c r="C44" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D44" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E44" s="36" t="s">
-        <v>116</v>
+      <c r="D44" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="21"/>
-      <c r="B45" s="16"/>
+      <c r="A45" s="25"/>
+      <c r="B45" s="28"/>
       <c r="C45" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D45" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E45" s="36" t="s">
-        <v>114</v>
+      <c r="D45" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="21"/>
-      <c r="B46" s="16"/>
+      <c r="A46" s="25"/>
+      <c r="B46" s="28"/>
       <c r="C46" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D46" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E46" s="36" t="s">
-        <v>116</v>
+      <c r="D46" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E46" s="17" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="21"/>
-      <c r="B47" s="32"/>
+      <c r="A47" s="25"/>
+      <c r="B47" s="29"/>
       <c r="C47" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D47" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E47" s="36" t="s">
-        <v>116</v>
+      <c r="D47" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="21"/>
-      <c r="B48" s="17" t="s">
+      <c r="A48" s="25"/>
+      <c r="B48" s="30" t="s">
         <v>58</v>
       </c>
       <c r="C48" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D48" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E48" s="36" t="s">
-        <v>114</v>
+      <c r="D48" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="21"/>
-      <c r="B49" s="18"/>
+      <c r="A49" s="25"/>
+      <c r="B49" s="31"/>
       <c r="C49" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D49" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E49" s="36" t="s">
-        <v>114</v>
+      <c r="D49" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="21"/>
-      <c r="B50" s="18"/>
+      <c r="A50" s="25"/>
+      <c r="B50" s="31"/>
       <c r="C50" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D50" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E50" s="36" t="s">
-        <v>114</v>
+      <c r="D50" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E50" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="21"/>
-      <c r="B51" s="18"/>
+      <c r="A51" s="25"/>
+      <c r="B51" s="31"/>
       <c r="C51" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D51" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E51" s="36" t="s">
-        <v>114</v>
+      <c r="D51" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="21"/>
-      <c r="B52" s="18"/>
+      <c r="A52" s="25"/>
+      <c r="B52" s="31"/>
       <c r="C52" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D52" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E52" s="36" t="s">
-        <v>114</v>
+      <c r="D52" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="21"/>
-      <c r="B53" s="18"/>
+      <c r="A53" s="25"/>
+      <c r="B53" s="31"/>
       <c r="C53" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D53" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E53" s="36" t="s">
-        <v>114</v>
+      <c r="D53" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="21"/>
-      <c r="B54" s="19"/>
+      <c r="A54" s="25"/>
+      <c r="B54" s="32"/>
       <c r="C54" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D54" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E54" s="36" t="s">
-        <v>114</v>
+      <c r="D54" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E54" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="21"/>
-      <c r="B55" s="15" t="s">
+      <c r="A55" s="25"/>
+      <c r="B55" s="27" t="s">
         <v>66</v>
       </c>
       <c r="C55" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="D55" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E55" s="36" t="s">
-        <v>114</v>
+      <c r="D55" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="21"/>
-      <c r="B56" s="16"/>
+      <c r="A56" s="25"/>
+      <c r="B56" s="28"/>
       <c r="C56" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D56" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="E56" s="36" t="s">
+      <c r="D56" s="20" t="s">
         <v>118</v>
       </c>
+      <c r="E56" s="17" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="21"/>
-      <c r="B57" s="16"/>
+      <c r="A57" s="25"/>
+      <c r="B57" s="28"/>
       <c r="C57" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="D57" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E57" s="36" t="s">
-        <v>114</v>
+      <c r="D57" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E57" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="21"/>
-      <c r="B58" s="16"/>
+      <c r="A58" s="25"/>
+      <c r="B58" s="28"/>
       <c r="C58" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D58" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E58" s="36" t="s">
-        <v>114</v>
+      <c r="D58" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E58" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="21"/>
-      <c r="B59" s="16"/>
+      <c r="A59" s="25"/>
+      <c r="B59" s="28"/>
       <c r="C59" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D59" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E59" s="36" t="s">
-        <v>116</v>
+      <c r="D59" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E59" s="17" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="21"/>
-      <c r="B60" s="16"/>
+      <c r="A60" s="25"/>
+      <c r="B60" s="28"/>
       <c r="C60" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="D60" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="E60" s="36" t="s">
+      <c r="D60" s="20" t="s">
         <v>118</v>
       </c>
+      <c r="E60" s="17" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="21"/>
-      <c r="B61" s="32"/>
+      <c r="A61" s="25"/>
+      <c r="B61" s="29"/>
       <c r="C61" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D61" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="E61" s="36" t="s">
+      <c r="D61" s="20" t="s">
         <v>118</v>
       </c>
+      <c r="E61" s="17" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="21"/>
-      <c r="B62" s="17" t="s">
+      <c r="A62" s="25"/>
+      <c r="B62" s="30" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E62" s="36" t="s">
-        <v>114</v>
+      <c r="D62" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E62" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="21"/>
-      <c r="B63" s="18"/>
+      <c r="A63" s="25"/>
+      <c r="B63" s="31"/>
       <c r="C63" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E63" s="36" t="s">
-        <v>114</v>
+      <c r="D63" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E63" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="21"/>
-      <c r="B64" s="18"/>
+      <c r="A64" s="25"/>
+      <c r="B64" s="31"/>
       <c r="C64" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D64" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E64" s="36" t="s">
-        <v>114</v>
+      <c r="D64" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E64" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="21"/>
-      <c r="B65" s="18"/>
+      <c r="A65" s="25"/>
+      <c r="B65" s="31"/>
       <c r="C65" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="D65" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E65" s="36" t="s">
-        <v>114</v>
+      <c r="D65" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E65" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="21"/>
-      <c r="B66" s="18"/>
+      <c r="A66" s="25"/>
+      <c r="B66" s="31"/>
       <c r="C66" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D66" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E66" s="36" t="s">
-        <v>114</v>
+      <c r="D66" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E66" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="21"/>
-      <c r="B67" s="18"/>
+      <c r="A67" s="25"/>
+      <c r="B67" s="31"/>
       <c r="C67" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="D67" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E67" s="36" t="s">
-        <v>114</v>
+      <c r="D67" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E67" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="21"/>
-      <c r="B68" s="18"/>
+      <c r="A68" s="25"/>
+      <c r="B68" s="31"/>
       <c r="C68" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="D68" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E68" s="36" t="s">
-        <v>114</v>
+      <c r="D68" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E68" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="21"/>
-      <c r="B69" s="18"/>
+      <c r="A69" s="25"/>
+      <c r="B69" s="31"/>
       <c r="C69" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="D69" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E69" s="36" t="s">
-        <v>114</v>
+      <c r="D69" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E69" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="21"/>
-      <c r="B70" s="18"/>
+      <c r="A70" s="25"/>
+      <c r="B70" s="31"/>
       <c r="C70" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="D70" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E70" s="36" t="s">
-        <v>114</v>
+      <c r="D70" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E70" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="21"/>
-      <c r="B71" s="18"/>
+      <c r="A71" s="25"/>
+      <c r="B71" s="31"/>
       <c r="C71" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D71" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="E71" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="D71" s="20" t="s">
         <v>118</v>
       </c>
+      <c r="E71" s="17" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="21"/>
-      <c r="B72" s="19"/>
+      <c r="A72" s="25"/>
+      <c r="B72" s="32"/>
       <c r="C72" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D72" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E72" s="36" t="s">
-        <v>114</v>
+      <c r="D72" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E72" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="21"/>
-      <c r="B73" s="15" t="s">
+      <c r="A73" s="25"/>
+      <c r="B73" s="27" t="s">
         <v>95</v>
       </c>
       <c r="C73" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="D73" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E73" s="36" t="s">
-        <v>114</v>
+      <c r="D73" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E73" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="21"/>
-      <c r="B74" s="16"/>
+      <c r="A74" s="25"/>
+      <c r="B74" s="28"/>
       <c r="C74" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="D74" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E74" s="36" t="s">
-        <v>114</v>
+      <c r="D74" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E74" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="21"/>
-      <c r="B75" s="32"/>
+      <c r="A75" s="25"/>
+      <c r="B75" s="29"/>
       <c r="C75" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D75" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E75" s="36" t="s">
-        <v>114</v>
+      <c r="D75" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E75" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="22"/>
-      <c r="B76" s="17" t="s">
+      <c r="A76" s="34"/>
+      <c r="B76" s="30" t="s">
         <v>87</v>
       </c>
       <c r="C76" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="D76" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="E76" s="36" t="s">
+      <c r="D76" s="20" t="s">
         <v>118</v>
       </c>
+      <c r="E76" s="17" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="22"/>
-      <c r="B77" s="18"/>
+      <c r="A77" s="34"/>
+      <c r="B77" s="31"/>
       <c r="C77" s="11"/>
-      <c r="D77" s="34"/>
-      <c r="E77" s="36"/>
+      <c r="D77" s="15"/>
+      <c r="E77" s="17"/>
     </row>
     <row r="78" spans="1:5">
-      <c r="A78" s="22"/>
-      <c r="B78" s="18"/>
+      <c r="A78" s="34"/>
+      <c r="B78" s="31"/>
       <c r="C78" s="11"/>
-      <c r="D78" s="34"/>
-      <c r="E78" s="36"/>
+      <c r="D78" s="15"/>
+      <c r="E78" s="17"/>
     </row>
     <row r="79" spans="1:5">
-      <c r="A79" s="22"/>
-      <c r="B79" s="18"/>
+      <c r="A79" s="34"/>
+      <c r="B79" s="31"/>
       <c r="C79" s="11"/>
-      <c r="D79" s="34"/>
-      <c r="E79" s="36"/>
+      <c r="D79" s="15"/>
+      <c r="E79" s="17"/>
     </row>
     <row r="80" spans="1:5">
-      <c r="A80" s="23"/>
-      <c r="B80" s="19"/>
+      <c r="A80" s="35"/>
+      <c r="B80" s="32"/>
       <c r="C80" s="11"/>
-      <c r="D80" s="34"/>
-      <c r="E80" s="36"/>
+      <c r="D80" s="15"/>
+      <c r="E80" s="17"/>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="24" t="s">
+      <c r="A81" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="B81" s="27"/>
+      <c r="B81" s="39"/>
       <c r="C81" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D81" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E81" s="36" t="s">
-        <v>114</v>
+      <c r="D81" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E81" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="25"/>
-      <c r="B82" s="28"/>
+      <c r="A82" s="37"/>
+      <c r="B82" s="40"/>
       <c r="C82" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="D82" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E82" s="36" t="s">
-        <v>114</v>
+        <v>112</v>
+      </c>
+      <c r="D82" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E82" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="25"/>
-      <c r="B83" s="28"/>
+      <c r="A83" s="37"/>
+      <c r="B83" s="40"/>
       <c r="C83" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E83" s="36" t="s">
-        <v>114</v>
+      <c r="D83" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E83" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="25"/>
-      <c r="B84" s="28"/>
+      <c r="A84" s="37"/>
+      <c r="B84" s="40"/>
       <c r="C84" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="D84" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E84" s="36" t="s">
-        <v>114</v>
+      <c r="D84" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E84" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="26"/>
-      <c r="B85" s="29"/>
+      <c r="A85" s="38"/>
+      <c r="B85" s="41"/>
       <c r="C85" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="D85" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E85" s="36" t="s">
-        <v>114</v>
+      <c r="D85" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E85" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="30" t="s">
+      <c r="A86" s="24" t="s">
         <v>82</v>
       </c>
       <c r="B86" s="6" t="s">
@@ -2490,120 +2490,122 @@
       <c r="C86" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="D86" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="E86" s="36" t="s">
-        <v>115</v>
+      <c r="D86" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="E86" s="17" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="87" spans="1:5">
-      <c r="A87" s="21"/>
+      <c r="A87" s="25"/>
       <c r="B87" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C87" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="D87" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="E87" s="36" t="s">
-        <v>115</v>
+      <c r="D87" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="E87" s="17" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="88" spans="1:5">
-      <c r="A88" s="21"/>
+      <c r="A88" s="25"/>
       <c r="B88" s="6" t="s">
         <v>93</v>
       </c>
       <c r="C88" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="D88" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="E88" s="36" t="s">
-        <v>115</v>
+      <c r="D88" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="E88" s="17" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="89" spans="1:5">
-      <c r="A89" s="21"/>
+      <c r="A89" s="25"/>
       <c r="B89" s="6" t="s">
         <v>94</v>
       </c>
       <c r="C89" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D89" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="E89" s="36" t="s">
-        <v>115</v>
+      <c r="D89" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="E89" s="17" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="21"/>
+      <c r="A90" s="25"/>
       <c r="B90" s="6" t="s">
         <v>101</v>
       </c>
       <c r="C90" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="D90" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="E90" s="36" t="s">
-        <v>115</v>
+      <c r="D90" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="E90" s="17" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="21"/>
+      <c r="A91" s="25"/>
       <c r="B91" s="6" t="s">
         <v>102</v>
       </c>
       <c r="C91" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="D91" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="E91" s="36" t="s">
-        <v>115</v>
+      <c r="D91" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="E91" s="17" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="31"/>
+      <c r="A92" s="26"/>
       <c r="B92" s="6" t="s">
         <v>100</v>
       </c>
       <c r="C92" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="D92" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="E92" s="36" t="s">
-        <v>115</v>
+      <c r="D92" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="E92" s="17" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5"/>
       <c r="B93" s="6"/>
       <c r="C93" s="9"/>
-      <c r="D93" s="34"/>
-      <c r="E93" s="36"/>
+      <c r="D93" s="15"/>
+      <c r="E93" s="17"/>
     </row>
     <row r="94" spans="1:5" ht="14.25" thickBot="1">
       <c r="A94" s="7"/>
       <c r="B94" s="8"/>
       <c r="C94" s="10"/>
-      <c r="D94" s="37"/>
-      <c r="E94" s="38"/>
+      <c r="D94" s="18"/>
+      <c r="E94" s="19"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:E92"/>
   <mergeCells count="18">
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B20:B24"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A86:A92"/>
     <mergeCell ref="B73:B75"/>
@@ -2620,8 +2622,6 @@
     <mergeCell ref="B3:B7"/>
     <mergeCell ref="B8:B10"/>
     <mergeCell ref="B11:B17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B20:B24"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/01.需求特性/版本特性列表.xlsx
+++ b/internal_doc/01.需求特性/版本特性列表.xlsx
@@ -992,6 +992,21 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1010,22 +1025,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1370,13 +1370,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="23"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="28"/>
     </row>
     <row r="2" spans="1:5" ht="26.25" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="s">
@@ -1413,8 +1413,8 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="25"/>
-      <c r="B4" s="31"/>
+      <c r="A4" s="30"/>
+      <c r="B4" s="24"/>
       <c r="C4" s="12" t="s">
         <v>17</v>
       </c>
@@ -1426,8 +1426,8 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="25"/>
-      <c r="B5" s="31"/>
+      <c r="A5" s="30"/>
+      <c r="B5" s="24"/>
       <c r="C5" s="11" t="s">
         <v>18</v>
       </c>
@@ -1439,8 +1439,8 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="25"/>
-      <c r="B6" s="31"/>
+      <c r="A6" s="30"/>
+      <c r="B6" s="24"/>
       <c r="C6" s="11" t="s">
         <v>19</v>
       </c>
@@ -1452,21 +1452,21 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="25"/>
-      <c r="B7" s="32"/>
+      <c r="A7" s="30"/>
+      <c r="B7" s="25"/>
       <c r="C7" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="25"/>
-      <c r="B8" s="27" t="s">
+      <c r="A8" s="30"/>
+      <c r="B8" s="21" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="13" t="s">
@@ -1480,8 +1480,8 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="25"/>
-      <c r="B9" s="28"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="32"/>
       <c r="C9" s="14" t="s">
         <v>22</v>
       </c>
@@ -1493,8 +1493,8 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="25"/>
-      <c r="B10" s="29"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="22"/>
       <c r="C10" s="13" t="s">
         <v>23</v>
       </c>
@@ -1506,8 +1506,8 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="25"/>
-      <c r="B11" s="30" t="s">
+      <c r="A11" s="30"/>
+      <c r="B11" s="23" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="11" t="s">
@@ -1521,8 +1521,8 @@
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="25"/>
-      <c r="B12" s="31"/>
+      <c r="A12" s="30"/>
+      <c r="B12" s="24"/>
       <c r="C12" s="11" t="s">
         <v>45</v>
       </c>
@@ -1534,8 +1534,8 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="25"/>
-      <c r="B13" s="31"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="24"/>
       <c r="C13" s="11" t="s">
         <v>46</v>
       </c>
@@ -1547,8 +1547,8 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="25"/>
-      <c r="B14" s="31"/>
+      <c r="A14" s="30"/>
+      <c r="B14" s="24"/>
       <c r="C14" s="11" t="s">
         <v>24</v>
       </c>
@@ -1560,8 +1560,8 @@
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="25"/>
-      <c r="B15" s="31"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="24"/>
       <c r="C15" s="11" t="s">
         <v>25</v>
       </c>
@@ -1573,8 +1573,8 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="25"/>
-      <c r="B16" s="31"/>
+      <c r="A16" s="30"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="11" t="s">
         <v>110</v>
       </c>
@@ -1586,8 +1586,8 @@
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="25"/>
-      <c r="B17" s="32"/>
+      <c r="A17" s="30"/>
+      <c r="B17" s="25"/>
       <c r="C17" s="11" t="s">
         <v>26</v>
       </c>
@@ -1599,8 +1599,8 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="25"/>
-      <c r="B18" s="27" t="s">
+      <c r="A18" s="30"/>
+      <c r="B18" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="13" t="s">
@@ -1614,8 +1614,8 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="25"/>
-      <c r="B19" s="29"/>
+      <c r="A19" s="30"/>
+      <c r="B19" s="22"/>
       <c r="C19" s="13" t="s">
         <v>28</v>
       </c>
@@ -1627,8 +1627,8 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="25"/>
-      <c r="B20" s="30" t="s">
+      <c r="A20" s="30"/>
+      <c r="B20" s="23" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="11" t="s">
@@ -1642,8 +1642,8 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="25"/>
-      <c r="B21" s="31"/>
+      <c r="A21" s="30"/>
+      <c r="B21" s="24"/>
       <c r="C21" s="11" t="s">
         <v>30</v>
       </c>
@@ -1655,8 +1655,8 @@
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="25"/>
-      <c r="B22" s="31"/>
+      <c r="A22" s="30"/>
+      <c r="B22" s="24"/>
       <c r="C22" s="11" t="s">
         <v>31</v>
       </c>
@@ -1668,8 +1668,8 @@
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="25"/>
-      <c r="B23" s="31"/>
+      <c r="A23" s="30"/>
+      <c r="B23" s="24"/>
       <c r="C23" s="11" t="s">
         <v>32</v>
       </c>
@@ -1681,8 +1681,8 @@
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="25"/>
-      <c r="B24" s="32"/>
+      <c r="A24" s="30"/>
+      <c r="B24" s="25"/>
       <c r="C24" s="11" t="s">
         <v>33</v>
       </c>
@@ -1694,8 +1694,8 @@
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="25"/>
-      <c r="B25" s="27" t="s">
+      <c r="A25" s="30"/>
+      <c r="B25" s="21" t="s">
         <v>13</v>
       </c>
       <c r="C25" s="13" t="s">
@@ -1709,8 +1709,8 @@
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="25"/>
-      <c r="B26" s="28"/>
+      <c r="A26" s="30"/>
+      <c r="B26" s="32"/>
       <c r="C26" s="13" t="s">
         <v>39</v>
       </c>
@@ -1722,8 +1722,8 @@
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="25"/>
-      <c r="B27" s="28"/>
+      <c r="A27" s="30"/>
+      <c r="B27" s="32"/>
       <c r="C27" s="13" t="s">
         <v>15</v>
       </c>
@@ -1735,8 +1735,8 @@
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="25"/>
-      <c r="B28" s="28"/>
+      <c r="A28" s="30"/>
+      <c r="B28" s="32"/>
       <c r="C28" s="13" t="s">
         <v>41</v>
       </c>
@@ -1748,8 +1748,8 @@
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="25"/>
-      <c r="B29" s="28"/>
+      <c r="A29" s="30"/>
+      <c r="B29" s="32"/>
       <c r="C29" s="13" t="s">
         <v>40</v>
       </c>
@@ -1761,8 +1761,8 @@
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="25"/>
-      <c r="B30" s="28"/>
+      <c r="A30" s="30"/>
+      <c r="B30" s="32"/>
       <c r="C30" s="13" t="s">
         <v>43</v>
       </c>
@@ -1774,8 +1774,8 @@
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="25"/>
-      <c r="B31" s="28"/>
+      <c r="A31" s="30"/>
+      <c r="B31" s="32"/>
       <c r="C31" s="13" t="s">
         <v>34</v>
       </c>
@@ -1787,8 +1787,8 @@
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="25"/>
-      <c r="B32" s="28"/>
+      <c r="A32" s="30"/>
+      <c r="B32" s="32"/>
       <c r="C32" s="13" t="s">
         <v>35</v>
       </c>
@@ -1800,8 +1800,8 @@
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="25"/>
-      <c r="B33" s="28"/>
+      <c r="A33" s="30"/>
+      <c r="B33" s="32"/>
       <c r="C33" s="13" t="s">
         <v>36</v>
       </c>
@@ -1813,8 +1813,8 @@
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="25"/>
-      <c r="B34" s="28"/>
+      <c r="A34" s="30"/>
+      <c r="B34" s="32"/>
       <c r="C34" s="13" t="s">
         <v>37</v>
       </c>
@@ -1826,8 +1826,8 @@
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="25"/>
-      <c r="B35" s="28"/>
+      <c r="A35" s="30"/>
+      <c r="B35" s="32"/>
       <c r="C35" s="13" t="s">
         <v>111</v>
       </c>
@@ -1839,8 +1839,8 @@
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="25"/>
-      <c r="B36" s="28"/>
+      <c r="A36" s="30"/>
+      <c r="B36" s="32"/>
       <c r="C36" s="13" t="s">
         <v>38</v>
       </c>
@@ -1852,8 +1852,8 @@
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="25"/>
-      <c r="B37" s="30" t="s">
+      <c r="A37" s="30"/>
+      <c r="B37" s="23" t="s">
         <v>44</v>
       </c>
       <c r="C37" s="11" t="s">
@@ -1867,8 +1867,8 @@
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="25"/>
-      <c r="B38" s="31"/>
+      <c r="A38" s="30"/>
+      <c r="B38" s="24"/>
       <c r="C38" s="11" t="s">
         <v>47</v>
       </c>
@@ -1880,8 +1880,8 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="25"/>
-      <c r="B39" s="31"/>
+      <c r="A39" s="30"/>
+      <c r="B39" s="24"/>
       <c r="C39" s="11" t="s">
         <v>48</v>
       </c>
@@ -1893,8 +1893,8 @@
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="25"/>
-      <c r="B40" s="32"/>
+      <c r="A40" s="30"/>
+      <c r="B40" s="25"/>
       <c r="C40" s="11" t="s">
         <v>80</v>
       </c>
@@ -1906,8 +1906,8 @@
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="25"/>
-      <c r="B41" s="27" t="s">
+      <c r="A41" s="30"/>
+      <c r="B41" s="21" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="13" t="s">
@@ -1921,8 +1921,8 @@
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="25"/>
-      <c r="B42" s="28"/>
+      <c r="A42" s="30"/>
+      <c r="B42" s="32"/>
       <c r="C42" s="13" t="s">
         <v>50</v>
       </c>
@@ -1934,8 +1934,8 @@
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="25"/>
-      <c r="B43" s="28"/>
+      <c r="A43" s="30"/>
+      <c r="B43" s="32"/>
       <c r="C43" s="13" t="s">
         <v>51</v>
       </c>
@@ -1947,8 +1947,8 @@
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="25"/>
-      <c r="B44" s="28"/>
+      <c r="A44" s="30"/>
+      <c r="B44" s="32"/>
       <c r="C44" s="13" t="s">
         <v>52</v>
       </c>
@@ -1960,8 +1960,8 @@
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="25"/>
-      <c r="B45" s="28"/>
+      <c r="A45" s="30"/>
+      <c r="B45" s="32"/>
       <c r="C45" s="13" t="s">
         <v>53</v>
       </c>
@@ -1973,8 +1973,8 @@
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="25"/>
-      <c r="B46" s="28"/>
+      <c r="A46" s="30"/>
+      <c r="B46" s="32"/>
       <c r="C46" s="13" t="s">
         <v>54</v>
       </c>
@@ -1986,8 +1986,8 @@
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="25"/>
-      <c r="B47" s="29"/>
+      <c r="A47" s="30"/>
+      <c r="B47" s="22"/>
       <c r="C47" s="13" t="s">
         <v>65</v>
       </c>
@@ -1999,8 +1999,8 @@
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="25"/>
-      <c r="B48" s="30" t="s">
+      <c r="A48" s="30"/>
+      <c r="B48" s="23" t="s">
         <v>58</v>
       </c>
       <c r="C48" s="11" t="s">
@@ -2014,8 +2014,8 @@
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="25"/>
-      <c r="B49" s="31"/>
+      <c r="A49" s="30"/>
+      <c r="B49" s="24"/>
       <c r="C49" s="11" t="s">
         <v>57</v>
       </c>
@@ -2027,8 +2027,8 @@
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="25"/>
-      <c r="B50" s="31"/>
+      <c r="A50" s="30"/>
+      <c r="B50" s="24"/>
       <c r="C50" s="11" t="s">
         <v>59</v>
       </c>
@@ -2040,8 +2040,8 @@
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="25"/>
-      <c r="B51" s="31"/>
+      <c r="A51" s="30"/>
+      <c r="B51" s="24"/>
       <c r="C51" s="11" t="s">
         <v>60</v>
       </c>
@@ -2053,8 +2053,8 @@
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="25"/>
-      <c r="B52" s="31"/>
+      <c r="A52" s="30"/>
+      <c r="B52" s="24"/>
       <c r="C52" s="11" t="s">
         <v>61</v>
       </c>
@@ -2066,8 +2066,8 @@
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="25"/>
-      <c r="B53" s="31"/>
+      <c r="A53" s="30"/>
+      <c r="B53" s="24"/>
       <c r="C53" s="11" t="s">
         <v>62</v>
       </c>
@@ -2079,8 +2079,8 @@
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="25"/>
-      <c r="B54" s="32"/>
+      <c r="A54" s="30"/>
+      <c r="B54" s="25"/>
       <c r="C54" s="11" t="s">
         <v>64</v>
       </c>
@@ -2092,8 +2092,8 @@
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="25"/>
-      <c r="B55" s="27" t="s">
+      <c r="A55" s="30"/>
+      <c r="B55" s="21" t="s">
         <v>66</v>
       </c>
       <c r="C55" s="13" t="s">
@@ -2107,8 +2107,8 @@
       </c>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="25"/>
-      <c r="B56" s="28"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="32"/>
       <c r="C56" s="13" t="s">
         <v>68</v>
       </c>
@@ -2120,8 +2120,8 @@
       </c>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="25"/>
-      <c r="B57" s="28"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="32"/>
       <c r="C57" s="13" t="s">
         <v>69</v>
       </c>
@@ -2133,8 +2133,8 @@
       </c>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="25"/>
-      <c r="B58" s="28"/>
+      <c r="A58" s="30"/>
+      <c r="B58" s="32"/>
       <c r="C58" s="13" t="s">
         <v>70</v>
       </c>
@@ -2146,8 +2146,8 @@
       </c>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="25"/>
-      <c r="B59" s="28"/>
+      <c r="A59" s="30"/>
+      <c r="B59" s="32"/>
       <c r="C59" s="13" t="s">
         <v>63</v>
       </c>
@@ -2159,8 +2159,8 @@
       </c>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="25"/>
-      <c r="B60" s="28"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="32"/>
       <c r="C60" s="13" t="s">
         <v>71</v>
       </c>
@@ -2172,8 +2172,8 @@
       </c>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="25"/>
-      <c r="B61" s="29"/>
+      <c r="A61" s="30"/>
+      <c r="B61" s="22"/>
       <c r="C61" s="13" t="s">
         <v>55</v>
       </c>
@@ -2185,8 +2185,8 @@
       </c>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="25"/>
-      <c r="B62" s="30" t="s">
+      <c r="A62" s="30"/>
+      <c r="B62" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="11" t="s">
@@ -2200,8 +2200,8 @@
       </c>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="25"/>
-      <c r="B63" s="31"/>
+      <c r="A63" s="30"/>
+      <c r="B63" s="24"/>
       <c r="C63" s="11" t="s">
         <v>73</v>
       </c>
@@ -2213,8 +2213,8 @@
       </c>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="25"/>
-      <c r="B64" s="31"/>
+      <c r="A64" s="30"/>
+      <c r="B64" s="24"/>
       <c r="C64" s="11" t="s">
         <v>74</v>
       </c>
@@ -2226,8 +2226,8 @@
       </c>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="25"/>
-      <c r="B65" s="31"/>
+      <c r="A65" s="30"/>
+      <c r="B65" s="24"/>
       <c r="C65" s="11" t="s">
         <v>75</v>
       </c>
@@ -2239,8 +2239,8 @@
       </c>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="25"/>
-      <c r="B66" s="31"/>
+      <c r="A66" s="30"/>
+      <c r="B66" s="24"/>
       <c r="C66" s="11" t="s">
         <v>76</v>
       </c>
@@ -2252,8 +2252,8 @@
       </c>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="25"/>
-      <c r="B67" s="31"/>
+      <c r="A67" s="30"/>
+      <c r="B67" s="24"/>
       <c r="C67" s="11" t="s">
         <v>78</v>
       </c>
@@ -2265,8 +2265,8 @@
       </c>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="25"/>
-      <c r="B68" s="31"/>
+      <c r="A68" s="30"/>
+      <c r="B68" s="24"/>
       <c r="C68" s="11" t="s">
         <v>77</v>
       </c>
@@ -2278,8 +2278,8 @@
       </c>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="25"/>
-      <c r="B69" s="31"/>
+      <c r="A69" s="30"/>
+      <c r="B69" s="24"/>
       <c r="C69" s="11" t="s">
         <v>83</v>
       </c>
@@ -2291,8 +2291,8 @@
       </c>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="25"/>
-      <c r="B70" s="31"/>
+      <c r="A70" s="30"/>
+      <c r="B70" s="24"/>
       <c r="C70" s="11" t="s">
         <v>84</v>
       </c>
@@ -2304,8 +2304,8 @@
       </c>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="25"/>
-      <c r="B71" s="31"/>
+      <c r="A71" s="30"/>
+      <c r="B71" s="24"/>
       <c r="C71" s="11" t="s">
         <v>120</v>
       </c>
@@ -2317,8 +2317,8 @@
       </c>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="25"/>
-      <c r="B72" s="32"/>
+      <c r="A72" s="30"/>
+      <c r="B72" s="25"/>
       <c r="C72" s="11" t="s">
         <v>79</v>
       </c>
@@ -2330,8 +2330,8 @@
       </c>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="25"/>
-      <c r="B73" s="27" t="s">
+      <c r="A73" s="30"/>
+      <c r="B73" s="21" t="s">
         <v>95</v>
       </c>
       <c r="C73" s="13" t="s">
@@ -2345,8 +2345,8 @@
       </c>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="25"/>
-      <c r="B74" s="28"/>
+      <c r="A74" s="30"/>
+      <c r="B74" s="32"/>
       <c r="C74" s="13" t="s">
         <v>98</v>
       </c>
@@ -2358,8 +2358,8 @@
       </c>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="25"/>
-      <c r="B75" s="29"/>
+      <c r="A75" s="30"/>
+      <c r="B75" s="22"/>
       <c r="C75" s="13" t="s">
         <v>97</v>
       </c>
@@ -2372,7 +2372,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="34"/>
-      <c r="B76" s="30" t="s">
+      <c r="B76" s="23" t="s">
         <v>87</v>
       </c>
       <c r="C76" s="11" t="s">
@@ -2387,28 +2387,28 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="34"/>
-      <c r="B77" s="31"/>
+      <c r="B77" s="24"/>
       <c r="C77" s="11"/>
       <c r="D77" s="15"/>
       <c r="E77" s="17"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="34"/>
-      <c r="B78" s="31"/>
+      <c r="B78" s="24"/>
       <c r="C78" s="11"/>
       <c r="D78" s="15"/>
       <c r="E78" s="17"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="34"/>
-      <c r="B79" s="31"/>
+      <c r="B79" s="24"/>
       <c r="C79" s="11"/>
       <c r="D79" s="15"/>
       <c r="E79" s="17"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="35"/>
-      <c r="B80" s="32"/>
+      <c r="B80" s="25"/>
       <c r="C80" s="11"/>
       <c r="D80" s="15"/>
       <c r="E80" s="17"/>
@@ -2481,7 +2481,7 @@
       </c>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="24" t="s">
+      <c r="A86" s="29" t="s">
         <v>82</v>
       </c>
       <c r="B86" s="6" t="s">
@@ -2498,7 +2498,7 @@
       </c>
     </row>
     <row r="87" spans="1:5">
-      <c r="A87" s="25"/>
+      <c r="A87" s="30"/>
       <c r="B87" s="6" t="s">
         <v>92</v>
       </c>
@@ -2513,7 +2513,7 @@
       </c>
     </row>
     <row r="88" spans="1:5">
-      <c r="A88" s="25"/>
+      <c r="A88" s="30"/>
       <c r="B88" s="6" t="s">
         <v>93</v>
       </c>
@@ -2528,7 +2528,7 @@
       </c>
     </row>
     <row r="89" spans="1:5">
-      <c r="A89" s="25"/>
+      <c r="A89" s="30"/>
       <c r="B89" s="6" t="s">
         <v>94</v>
       </c>
@@ -2543,7 +2543,7 @@
       </c>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="25"/>
+      <c r="A90" s="30"/>
       <c r="B90" s="6" t="s">
         <v>101</v>
       </c>
@@ -2558,7 +2558,7 @@
       </c>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="25"/>
+      <c r="A91" s="30"/>
       <c r="B91" s="6" t="s">
         <v>102</v>
       </c>
@@ -2573,7 +2573,7 @@
       </c>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="26"/>
+      <c r="A92" s="31"/>
       <c r="B92" s="6" t="s">
         <v>100</v>
       </c>
@@ -2604,6 +2604,8 @@
   </sheetData>
   <autoFilter ref="A2:E92"/>
   <mergeCells count="18">
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B17"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="B20:B24"/>
     <mergeCell ref="A1:E1"/>
@@ -2620,8 +2622,6 @@
     <mergeCell ref="A81:A85"/>
     <mergeCell ref="B81:B85"/>
     <mergeCell ref="B3:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/01.需求特性/版本特性列表.xlsx
+++ b/internal_doc/01.需求特性/版本特性列表.xlsx
@@ -995,6 +995,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1023,9 +1026,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1370,13 +1370,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="28"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="29"/>
     </row>
     <row r="2" spans="1:5" ht="26.25" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="s">
@@ -1413,8 +1413,8 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="30"/>
-      <c r="B4" s="24"/>
+      <c r="A4" s="31"/>
+      <c r="B4" s="25"/>
       <c r="C4" s="12" t="s">
         <v>17</v>
       </c>
@@ -1426,8 +1426,8 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="30"/>
-      <c r="B5" s="24"/>
+      <c r="A5" s="31"/>
+      <c r="B5" s="25"/>
       <c r="C5" s="11" t="s">
         <v>18</v>
       </c>
@@ -1439,8 +1439,8 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="30"/>
-      <c r="B6" s="24"/>
+      <c r="A6" s="31"/>
+      <c r="B6" s="25"/>
       <c r="C6" s="11" t="s">
         <v>19</v>
       </c>
@@ -1452,8 +1452,8 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="30"/>
-      <c r="B7" s="25"/>
+      <c r="A7" s="31"/>
+      <c r="B7" s="26"/>
       <c r="C7" s="11" t="s">
         <v>20</v>
       </c>
@@ -1465,7 +1465,7 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="30"/>
+      <c r="A8" s="31"/>
       <c r="B8" s="21" t="s">
         <v>7</v>
       </c>
@@ -1480,8 +1480,8 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="30"/>
-      <c r="B9" s="32"/>
+      <c r="A9" s="31"/>
+      <c r="B9" s="22"/>
       <c r="C9" s="14" t="s">
         <v>22</v>
       </c>
@@ -1493,8 +1493,8 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="30"/>
-      <c r="B10" s="22"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="23"/>
       <c r="C10" s="13" t="s">
         <v>23</v>
       </c>
@@ -1506,8 +1506,8 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="30"/>
-      <c r="B11" s="23" t="s">
+      <c r="A11" s="31"/>
+      <c r="B11" s="24" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="11" t="s">
@@ -1521,8 +1521,8 @@
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="30"/>
-      <c r="B12" s="24"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="25"/>
       <c r="C12" s="11" t="s">
         <v>45</v>
       </c>
@@ -1534,8 +1534,8 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="30"/>
-      <c r="B13" s="24"/>
+      <c r="A13" s="31"/>
+      <c r="B13" s="25"/>
       <c r="C13" s="11" t="s">
         <v>46</v>
       </c>
@@ -1547,8 +1547,8 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="30"/>
-      <c r="B14" s="24"/>
+      <c r="A14" s="31"/>
+      <c r="B14" s="25"/>
       <c r="C14" s="11" t="s">
         <v>24</v>
       </c>
@@ -1560,8 +1560,8 @@
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="30"/>
-      <c r="B15" s="24"/>
+      <c r="A15" s="31"/>
+      <c r="B15" s="25"/>
       <c r="C15" s="11" t="s">
         <v>25</v>
       </c>
@@ -1573,8 +1573,8 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="30"/>
-      <c r="B16" s="24"/>
+      <c r="A16" s="31"/>
+      <c r="B16" s="25"/>
       <c r="C16" s="11" t="s">
         <v>110</v>
       </c>
@@ -1586,8 +1586,8 @@
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="30"/>
-      <c r="B17" s="25"/>
+      <c r="A17" s="31"/>
+      <c r="B17" s="26"/>
       <c r="C17" s="11" t="s">
         <v>26</v>
       </c>
@@ -1599,7 +1599,7 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="30"/>
+      <c r="A18" s="31"/>
       <c r="B18" s="21" t="s">
         <v>9</v>
       </c>
@@ -1614,8 +1614,8 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="30"/>
-      <c r="B19" s="22"/>
+      <c r="A19" s="31"/>
+      <c r="B19" s="23"/>
       <c r="C19" s="13" t="s">
         <v>28</v>
       </c>
@@ -1627,8 +1627,8 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="30"/>
-      <c r="B20" s="23" t="s">
+      <c r="A20" s="31"/>
+      <c r="B20" s="24" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="11" t="s">
@@ -1642,8 +1642,8 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="30"/>
-      <c r="B21" s="24"/>
+      <c r="A21" s="31"/>
+      <c r="B21" s="25"/>
       <c r="C21" s="11" t="s">
         <v>30</v>
       </c>
@@ -1655,8 +1655,8 @@
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="30"/>
-      <c r="B22" s="24"/>
+      <c r="A22" s="31"/>
+      <c r="B22" s="25"/>
       <c r="C22" s="11" t="s">
         <v>31</v>
       </c>
@@ -1668,8 +1668,8 @@
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="30"/>
-      <c r="B23" s="24"/>
+      <c r="A23" s="31"/>
+      <c r="B23" s="25"/>
       <c r="C23" s="11" t="s">
         <v>32</v>
       </c>
@@ -1681,8 +1681,8 @@
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="30"/>
-      <c r="B24" s="25"/>
+      <c r="A24" s="31"/>
+      <c r="B24" s="26"/>
       <c r="C24" s="11" t="s">
         <v>33</v>
       </c>
@@ -1694,7 +1694,7 @@
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="30"/>
+      <c r="A25" s="31"/>
       <c r="B25" s="21" t="s">
         <v>13</v>
       </c>
@@ -1709,8 +1709,8 @@
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="30"/>
-      <c r="B26" s="32"/>
+      <c r="A26" s="31"/>
+      <c r="B26" s="22"/>
       <c r="C26" s="13" t="s">
         <v>39</v>
       </c>
@@ -1722,8 +1722,8 @@
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="30"/>
-      <c r="B27" s="32"/>
+      <c r="A27" s="31"/>
+      <c r="B27" s="22"/>
       <c r="C27" s="13" t="s">
         <v>15</v>
       </c>
@@ -1735,8 +1735,8 @@
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="30"/>
-      <c r="B28" s="32"/>
+      <c r="A28" s="31"/>
+      <c r="B28" s="22"/>
       <c r="C28" s="13" t="s">
         <v>41</v>
       </c>
@@ -1748,8 +1748,8 @@
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="30"/>
-      <c r="B29" s="32"/>
+      <c r="A29" s="31"/>
+      <c r="B29" s="22"/>
       <c r="C29" s="13" t="s">
         <v>40</v>
       </c>
@@ -1761,8 +1761,8 @@
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="30"/>
-      <c r="B30" s="32"/>
+      <c r="A30" s="31"/>
+      <c r="B30" s="22"/>
       <c r="C30" s="13" t="s">
         <v>43</v>
       </c>
@@ -1774,8 +1774,8 @@
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="30"/>
-      <c r="B31" s="32"/>
+      <c r="A31" s="31"/>
+      <c r="B31" s="22"/>
       <c r="C31" s="13" t="s">
         <v>34</v>
       </c>
@@ -1787,8 +1787,8 @@
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="30"/>
-      <c r="B32" s="32"/>
+      <c r="A32" s="31"/>
+      <c r="B32" s="22"/>
       <c r="C32" s="13" t="s">
         <v>35</v>
       </c>
@@ -1800,8 +1800,8 @@
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="30"/>
-      <c r="B33" s="32"/>
+      <c r="A33" s="31"/>
+      <c r="B33" s="22"/>
       <c r="C33" s="13" t="s">
         <v>36</v>
       </c>
@@ -1813,8 +1813,8 @@
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="30"/>
-      <c r="B34" s="32"/>
+      <c r="A34" s="31"/>
+      <c r="B34" s="22"/>
       <c r="C34" s="13" t="s">
         <v>37</v>
       </c>
@@ -1826,8 +1826,8 @@
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="30"/>
-      <c r="B35" s="32"/>
+      <c r="A35" s="31"/>
+      <c r="B35" s="22"/>
       <c r="C35" s="13" t="s">
         <v>111</v>
       </c>
@@ -1839,8 +1839,8 @@
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="30"/>
-      <c r="B36" s="32"/>
+      <c r="A36" s="31"/>
+      <c r="B36" s="22"/>
       <c r="C36" s="13" t="s">
         <v>38</v>
       </c>
@@ -1852,8 +1852,8 @@
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="30"/>
-      <c r="B37" s="23" t="s">
+      <c r="A37" s="31"/>
+      <c r="B37" s="24" t="s">
         <v>44</v>
       </c>
       <c r="C37" s="11" t="s">
@@ -1867,8 +1867,8 @@
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="30"/>
-      <c r="B38" s="24"/>
+      <c r="A38" s="31"/>
+      <c r="B38" s="25"/>
       <c r="C38" s="11" t="s">
         <v>47</v>
       </c>
@@ -1880,8 +1880,8 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="30"/>
-      <c r="B39" s="24"/>
+      <c r="A39" s="31"/>
+      <c r="B39" s="25"/>
       <c r="C39" s="11" t="s">
         <v>48</v>
       </c>
@@ -1893,8 +1893,8 @@
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="30"/>
-      <c r="B40" s="25"/>
+      <c r="A40" s="31"/>
+      <c r="B40" s="26"/>
       <c r="C40" s="11" t="s">
         <v>80</v>
       </c>
@@ -1906,7 +1906,7 @@
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="30"/>
+      <c r="A41" s="31"/>
       <c r="B41" s="21" t="s">
         <v>10</v>
       </c>
@@ -1921,8 +1921,8 @@
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="30"/>
-      <c r="B42" s="32"/>
+      <c r="A42" s="31"/>
+      <c r="B42" s="22"/>
       <c r="C42" s="13" t="s">
         <v>50</v>
       </c>
@@ -1934,8 +1934,8 @@
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="30"/>
-      <c r="B43" s="32"/>
+      <c r="A43" s="31"/>
+      <c r="B43" s="22"/>
       <c r="C43" s="13" t="s">
         <v>51</v>
       </c>
@@ -1947,8 +1947,8 @@
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="30"/>
-      <c r="B44" s="32"/>
+      <c r="A44" s="31"/>
+      <c r="B44" s="22"/>
       <c r="C44" s="13" t="s">
         <v>52</v>
       </c>
@@ -1960,8 +1960,8 @@
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="30"/>
-      <c r="B45" s="32"/>
+      <c r="A45" s="31"/>
+      <c r="B45" s="22"/>
       <c r="C45" s="13" t="s">
         <v>53</v>
       </c>
@@ -1973,8 +1973,8 @@
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="30"/>
-      <c r="B46" s="32"/>
+      <c r="A46" s="31"/>
+      <c r="B46" s="22"/>
       <c r="C46" s="13" t="s">
         <v>54</v>
       </c>
@@ -1986,8 +1986,8 @@
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="30"/>
-      <c r="B47" s="22"/>
+      <c r="A47" s="31"/>
+      <c r="B47" s="23"/>
       <c r="C47" s="13" t="s">
         <v>65</v>
       </c>
@@ -1999,8 +1999,8 @@
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="30"/>
-      <c r="B48" s="23" t="s">
+      <c r="A48" s="31"/>
+      <c r="B48" s="24" t="s">
         <v>58</v>
       </c>
       <c r="C48" s="11" t="s">
@@ -2014,8 +2014,8 @@
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="30"/>
-      <c r="B49" s="24"/>
+      <c r="A49" s="31"/>
+      <c r="B49" s="25"/>
       <c r="C49" s="11" t="s">
         <v>57</v>
       </c>
@@ -2027,8 +2027,8 @@
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="30"/>
-      <c r="B50" s="24"/>
+      <c r="A50" s="31"/>
+      <c r="B50" s="25"/>
       <c r="C50" s="11" t="s">
         <v>59</v>
       </c>
@@ -2040,8 +2040,8 @@
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="30"/>
-      <c r="B51" s="24"/>
+      <c r="A51" s="31"/>
+      <c r="B51" s="25"/>
       <c r="C51" s="11" t="s">
         <v>60</v>
       </c>
@@ -2053,8 +2053,8 @@
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="30"/>
-      <c r="B52" s="24"/>
+      <c r="A52" s="31"/>
+      <c r="B52" s="25"/>
       <c r="C52" s="11" t="s">
         <v>61</v>
       </c>
@@ -2066,8 +2066,8 @@
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="30"/>
-      <c r="B53" s="24"/>
+      <c r="A53" s="31"/>
+      <c r="B53" s="25"/>
       <c r="C53" s="11" t="s">
         <v>62</v>
       </c>
@@ -2079,8 +2079,8 @@
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="30"/>
-      <c r="B54" s="25"/>
+      <c r="A54" s="31"/>
+      <c r="B54" s="26"/>
       <c r="C54" s="11" t="s">
         <v>64</v>
       </c>
@@ -2092,7 +2092,7 @@
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="30"/>
+      <c r="A55" s="31"/>
       <c r="B55" s="21" t="s">
         <v>66</v>
       </c>
@@ -2103,12 +2103,12 @@
         <v>115</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="30"/>
-      <c r="B56" s="32"/>
+      <c r="A56" s="31"/>
+      <c r="B56" s="22"/>
       <c r="C56" s="13" t="s">
         <v>68</v>
       </c>
@@ -2120,8 +2120,8 @@
       </c>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="30"/>
-      <c r="B57" s="32"/>
+      <c r="A57" s="31"/>
+      <c r="B57" s="22"/>
       <c r="C57" s="13" t="s">
         <v>69</v>
       </c>
@@ -2133,8 +2133,8 @@
       </c>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="30"/>
-      <c r="B58" s="32"/>
+      <c r="A58" s="31"/>
+      <c r="B58" s="22"/>
       <c r="C58" s="13" t="s">
         <v>70</v>
       </c>
@@ -2146,8 +2146,8 @@
       </c>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="30"/>
-      <c r="B59" s="32"/>
+      <c r="A59" s="31"/>
+      <c r="B59" s="22"/>
       <c r="C59" s="13" t="s">
         <v>63</v>
       </c>
@@ -2159,8 +2159,8 @@
       </c>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="30"/>
-      <c r="B60" s="32"/>
+      <c r="A60" s="31"/>
+      <c r="B60" s="22"/>
       <c r="C60" s="13" t="s">
         <v>71</v>
       </c>
@@ -2172,8 +2172,8 @@
       </c>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="30"/>
-      <c r="B61" s="22"/>
+      <c r="A61" s="31"/>
+      <c r="B61" s="23"/>
       <c r="C61" s="13" t="s">
         <v>55</v>
       </c>
@@ -2185,8 +2185,8 @@
       </c>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="30"/>
-      <c r="B62" s="23" t="s">
+      <c r="A62" s="31"/>
+      <c r="B62" s="24" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="11" t="s">
@@ -2200,8 +2200,8 @@
       </c>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="30"/>
-      <c r="B63" s="24"/>
+      <c r="A63" s="31"/>
+      <c r="B63" s="25"/>
       <c r="C63" s="11" t="s">
         <v>73</v>
       </c>
@@ -2213,8 +2213,8 @@
       </c>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="30"/>
-      <c r="B64" s="24"/>
+      <c r="A64" s="31"/>
+      <c r="B64" s="25"/>
       <c r="C64" s="11" t="s">
         <v>74</v>
       </c>
@@ -2226,8 +2226,8 @@
       </c>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="30"/>
-      <c r="B65" s="24"/>
+      <c r="A65" s="31"/>
+      <c r="B65" s="25"/>
       <c r="C65" s="11" t="s">
         <v>75</v>
       </c>
@@ -2239,8 +2239,8 @@
       </c>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="30"/>
-      <c r="B66" s="24"/>
+      <c r="A66" s="31"/>
+      <c r="B66" s="25"/>
       <c r="C66" s="11" t="s">
         <v>76</v>
       </c>
@@ -2252,8 +2252,8 @@
       </c>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="30"/>
-      <c r="B67" s="24"/>
+      <c r="A67" s="31"/>
+      <c r="B67" s="25"/>
       <c r="C67" s="11" t="s">
         <v>78</v>
       </c>
@@ -2265,8 +2265,8 @@
       </c>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="30"/>
-      <c r="B68" s="24"/>
+      <c r="A68" s="31"/>
+      <c r="B68" s="25"/>
       <c r="C68" s="11" t="s">
         <v>77</v>
       </c>
@@ -2278,8 +2278,8 @@
       </c>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="30"/>
-      <c r="B69" s="24"/>
+      <c r="A69" s="31"/>
+      <c r="B69" s="25"/>
       <c r="C69" s="11" t="s">
         <v>83</v>
       </c>
@@ -2291,8 +2291,8 @@
       </c>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="30"/>
-      <c r="B70" s="24"/>
+      <c r="A70" s="31"/>
+      <c r="B70" s="25"/>
       <c r="C70" s="11" t="s">
         <v>84</v>
       </c>
@@ -2304,8 +2304,8 @@
       </c>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="30"/>
-      <c r="B71" s="24"/>
+      <c r="A71" s="31"/>
+      <c r="B71" s="25"/>
       <c r="C71" s="11" t="s">
         <v>120</v>
       </c>
@@ -2317,8 +2317,8 @@
       </c>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="30"/>
-      <c r="B72" s="25"/>
+      <c r="A72" s="31"/>
+      <c r="B72" s="26"/>
       <c r="C72" s="11" t="s">
         <v>79</v>
       </c>
@@ -2330,7 +2330,7 @@
       </c>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="30"/>
+      <c r="A73" s="31"/>
       <c r="B73" s="21" t="s">
         <v>95</v>
       </c>
@@ -2345,8 +2345,8 @@
       </c>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="30"/>
-      <c r="B74" s="32"/>
+      <c r="A74" s="31"/>
+      <c r="B74" s="22"/>
       <c r="C74" s="13" t="s">
         <v>98</v>
       </c>
@@ -2358,8 +2358,8 @@
       </c>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="30"/>
-      <c r="B75" s="22"/>
+      <c r="A75" s="31"/>
+      <c r="B75" s="23"/>
       <c r="C75" s="13" t="s">
         <v>97</v>
       </c>
@@ -2372,7 +2372,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="34"/>
-      <c r="B76" s="23" t="s">
+      <c r="B76" s="24" t="s">
         <v>87</v>
       </c>
       <c r="C76" s="11" t="s">
@@ -2387,28 +2387,28 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="34"/>
-      <c r="B77" s="24"/>
+      <c r="B77" s="25"/>
       <c r="C77" s="11"/>
       <c r="D77" s="15"/>
       <c r="E77" s="17"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="34"/>
-      <c r="B78" s="24"/>
+      <c r="B78" s="25"/>
       <c r="C78" s="11"/>
       <c r="D78" s="15"/>
       <c r="E78" s="17"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="34"/>
-      <c r="B79" s="24"/>
+      <c r="B79" s="25"/>
       <c r="C79" s="11"/>
       <c r="D79" s="15"/>
       <c r="E79" s="17"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="35"/>
-      <c r="B80" s="25"/>
+      <c r="B80" s="26"/>
       <c r="C80" s="11"/>
       <c r="D80" s="15"/>
       <c r="E80" s="17"/>
@@ -2481,7 +2481,7 @@
       </c>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="29" t="s">
+      <c r="A86" s="30" t="s">
         <v>82</v>
       </c>
       <c r="B86" s="6" t="s">
@@ -2498,7 +2498,7 @@
       </c>
     </row>
     <row r="87" spans="1:5">
-      <c r="A87" s="30"/>
+      <c r="A87" s="31"/>
       <c r="B87" s="6" t="s">
         <v>92</v>
       </c>
@@ -2513,7 +2513,7 @@
       </c>
     </row>
     <row r="88" spans="1:5">
-      <c r="A88" s="30"/>
+      <c r="A88" s="31"/>
       <c r="B88" s="6" t="s">
         <v>93</v>
       </c>
@@ -2528,7 +2528,7 @@
       </c>
     </row>
     <row r="89" spans="1:5">
-      <c r="A89" s="30"/>
+      <c r="A89" s="31"/>
       <c r="B89" s="6" t="s">
         <v>94</v>
       </c>
@@ -2543,7 +2543,7 @@
       </c>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="30"/>
+      <c r="A90" s="31"/>
       <c r="B90" s="6" t="s">
         <v>101</v>
       </c>
@@ -2558,7 +2558,7 @@
       </c>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="30"/>
+      <c r="A91" s="31"/>
       <c r="B91" s="6" t="s">
         <v>102</v>
       </c>
@@ -2573,7 +2573,7 @@
       </c>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="31"/>
+      <c r="A92" s="32"/>
       <c r="B92" s="6" t="s">
         <v>100</v>
       </c>
@@ -2604,11 +2604,12 @@
   </sheetData>
   <autoFilter ref="A2:E92"/>
   <mergeCells count="18">
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B20:B24"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B25:B36"/>
+    <mergeCell ref="B76:B80"/>
+    <mergeCell ref="A3:A80"/>
+    <mergeCell ref="A81:A85"/>
+    <mergeCell ref="B81:B85"/>
+    <mergeCell ref="B3:B7"/>
     <mergeCell ref="A86:A92"/>
     <mergeCell ref="B73:B75"/>
     <mergeCell ref="B37:B40"/>
@@ -2616,12 +2617,11 @@
     <mergeCell ref="B48:B54"/>
     <mergeCell ref="B55:B61"/>
     <mergeCell ref="B62:B72"/>
-    <mergeCell ref="B25:B36"/>
-    <mergeCell ref="B76:B80"/>
-    <mergeCell ref="A3:A80"/>
-    <mergeCell ref="A81:A85"/>
-    <mergeCell ref="B81:B85"/>
-    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B20:B24"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/01.需求特性/版本特性列表.xlsx
+++ b/internal_doc/01.需求特性/版本特性列表.xlsx
@@ -998,16 +998,55 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1018,45 +1057,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1370,13 +1370,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="29"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="42"/>
     </row>
     <row r="2" spans="1:5" ht="26.25" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="s">
@@ -1396,10 +1396,10 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="14.25" thickTop="1">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="36" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="12" t="s">
@@ -1413,8 +1413,8 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="31"/>
-      <c r="B4" s="25"/>
+      <c r="A4" s="27"/>
+      <c r="B4" s="24"/>
       <c r="C4" s="12" t="s">
         <v>17</v>
       </c>
@@ -1426,8 +1426,8 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="31"/>
-      <c r="B5" s="25"/>
+      <c r="A5" s="27"/>
+      <c r="B5" s="24"/>
       <c r="C5" s="11" t="s">
         <v>18</v>
       </c>
@@ -1439,8 +1439,8 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="31"/>
-      <c r="B6" s="25"/>
+      <c r="A6" s="27"/>
+      <c r="B6" s="24"/>
       <c r="C6" s="11" t="s">
         <v>19</v>
       </c>
@@ -1452,8 +1452,8 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="31"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="25"/>
       <c r="C7" s="11" t="s">
         <v>20</v>
       </c>
@@ -1465,7 +1465,7 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="31"/>
+      <c r="A8" s="27"/>
       <c r="B8" s="21" t="s">
         <v>7</v>
       </c>
@@ -1480,7 +1480,7 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="31"/>
+      <c r="A9" s="27"/>
       <c r="B9" s="22"/>
       <c r="C9" s="14" t="s">
         <v>22</v>
@@ -1493,8 +1493,8 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="31"/>
-      <c r="B10" s="23"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="39"/>
       <c r="C10" s="13" t="s">
         <v>23</v>
       </c>
@@ -1506,8 +1506,8 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="31"/>
-      <c r="B11" s="24" t="s">
+      <c r="A11" s="27"/>
+      <c r="B11" s="23" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="11" t="s">
@@ -1521,8 +1521,8 @@
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="31"/>
-      <c r="B12" s="25"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="24"/>
       <c r="C12" s="11" t="s">
         <v>45</v>
       </c>
@@ -1534,8 +1534,8 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="31"/>
-      <c r="B13" s="25"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="24"/>
       <c r="C13" s="11" t="s">
         <v>46</v>
       </c>
@@ -1547,8 +1547,8 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="31"/>
-      <c r="B14" s="25"/>
+      <c r="A14" s="27"/>
+      <c r="B14" s="24"/>
       <c r="C14" s="11" t="s">
         <v>24</v>
       </c>
@@ -1560,8 +1560,8 @@
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="31"/>
-      <c r="B15" s="25"/>
+      <c r="A15" s="27"/>
+      <c r="B15" s="24"/>
       <c r="C15" s="11" t="s">
         <v>25</v>
       </c>
@@ -1573,8 +1573,8 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="31"/>
-      <c r="B16" s="25"/>
+      <c r="A16" s="27"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="11" t="s">
         <v>110</v>
       </c>
@@ -1586,8 +1586,8 @@
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="31"/>
-      <c r="B17" s="26"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="25"/>
       <c r="C17" s="11" t="s">
         <v>26</v>
       </c>
@@ -1599,7 +1599,7 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="31"/>
+      <c r="A18" s="27"/>
       <c r="B18" s="21" t="s">
         <v>9</v>
       </c>
@@ -1614,8 +1614,8 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="31"/>
-      <c r="B19" s="23"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="39"/>
       <c r="C19" s="13" t="s">
         <v>28</v>
       </c>
@@ -1627,8 +1627,8 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="31"/>
-      <c r="B20" s="24" t="s">
+      <c r="A20" s="27"/>
+      <c r="B20" s="23" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="11" t="s">
@@ -1642,8 +1642,8 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="31"/>
-      <c r="B21" s="25"/>
+      <c r="A21" s="27"/>
+      <c r="B21" s="24"/>
       <c r="C21" s="11" t="s">
         <v>30</v>
       </c>
@@ -1655,8 +1655,8 @@
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="31"/>
-      <c r="B22" s="25"/>
+      <c r="A22" s="27"/>
+      <c r="B22" s="24"/>
       <c r="C22" s="11" t="s">
         <v>31</v>
       </c>
@@ -1668,8 +1668,8 @@
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="31"/>
-      <c r="B23" s="25"/>
+      <c r="A23" s="27"/>
+      <c r="B23" s="24"/>
       <c r="C23" s="11" t="s">
         <v>32</v>
       </c>
@@ -1681,8 +1681,8 @@
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="31"/>
-      <c r="B24" s="26"/>
+      <c r="A24" s="27"/>
+      <c r="B24" s="25"/>
       <c r="C24" s="11" t="s">
         <v>33</v>
       </c>
@@ -1694,7 +1694,7 @@
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="31"/>
+      <c r="A25" s="27"/>
       <c r="B25" s="21" t="s">
         <v>13</v>
       </c>
@@ -1709,7 +1709,7 @@
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="31"/>
+      <c r="A26" s="27"/>
       <c r="B26" s="22"/>
       <c r="C26" s="13" t="s">
         <v>39</v>
@@ -1722,7 +1722,7 @@
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="31"/>
+      <c r="A27" s="27"/>
       <c r="B27" s="22"/>
       <c r="C27" s="13" t="s">
         <v>15</v>
@@ -1735,7 +1735,7 @@
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="31"/>
+      <c r="A28" s="27"/>
       <c r="B28" s="22"/>
       <c r="C28" s="13" t="s">
         <v>41</v>
@@ -1748,7 +1748,7 @@
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="31"/>
+      <c r="A29" s="27"/>
       <c r="B29" s="22"/>
       <c r="C29" s="13" t="s">
         <v>40</v>
@@ -1761,7 +1761,7 @@
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="31"/>
+      <c r="A30" s="27"/>
       <c r="B30" s="22"/>
       <c r="C30" s="13" t="s">
         <v>43</v>
@@ -1774,7 +1774,7 @@
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="31"/>
+      <c r="A31" s="27"/>
       <c r="B31" s="22"/>
       <c r="C31" s="13" t="s">
         <v>34</v>
@@ -1787,7 +1787,7 @@
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="31"/>
+      <c r="A32" s="27"/>
       <c r="B32" s="22"/>
       <c r="C32" s="13" t="s">
         <v>35</v>
@@ -1800,7 +1800,7 @@
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="31"/>
+      <c r="A33" s="27"/>
       <c r="B33" s="22"/>
       <c r="C33" s="13" t="s">
         <v>36</v>
@@ -1813,7 +1813,7 @@
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="31"/>
+      <c r="A34" s="27"/>
       <c r="B34" s="22"/>
       <c r="C34" s="13" t="s">
         <v>37</v>
@@ -1826,7 +1826,7 @@
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="31"/>
+      <c r="A35" s="27"/>
       <c r="B35" s="22"/>
       <c r="C35" s="13" t="s">
         <v>111</v>
@@ -1839,7 +1839,7 @@
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="31"/>
+      <c r="A36" s="27"/>
       <c r="B36" s="22"/>
       <c r="C36" s="13" t="s">
         <v>38</v>
@@ -1852,8 +1852,8 @@
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="31"/>
-      <c r="B37" s="24" t="s">
+      <c r="A37" s="27"/>
+      <c r="B37" s="23" t="s">
         <v>44</v>
       </c>
       <c r="C37" s="11" t="s">
@@ -1867,8 +1867,8 @@
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="31"/>
-      <c r="B38" s="25"/>
+      <c r="A38" s="27"/>
+      <c r="B38" s="24"/>
       <c r="C38" s="11" t="s">
         <v>47</v>
       </c>
@@ -1880,8 +1880,8 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="31"/>
-      <c r="B39" s="25"/>
+      <c r="A39" s="27"/>
+      <c r="B39" s="24"/>
       <c r="C39" s="11" t="s">
         <v>48</v>
       </c>
@@ -1893,8 +1893,8 @@
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="31"/>
-      <c r="B40" s="26"/>
+      <c r="A40" s="27"/>
+      <c r="B40" s="25"/>
       <c r="C40" s="11" t="s">
         <v>80</v>
       </c>
@@ -1906,7 +1906,7 @@
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="31"/>
+      <c r="A41" s="27"/>
       <c r="B41" s="21" t="s">
         <v>10</v>
       </c>
@@ -1921,7 +1921,7 @@
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="31"/>
+      <c r="A42" s="27"/>
       <c r="B42" s="22"/>
       <c r="C42" s="13" t="s">
         <v>50</v>
@@ -1934,7 +1934,7 @@
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="31"/>
+      <c r="A43" s="27"/>
       <c r="B43" s="22"/>
       <c r="C43" s="13" t="s">
         <v>51</v>
@@ -1947,7 +1947,7 @@
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="31"/>
+      <c r="A44" s="27"/>
       <c r="B44" s="22"/>
       <c r="C44" s="13" t="s">
         <v>52</v>
@@ -1960,7 +1960,7 @@
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="31"/>
+      <c r="A45" s="27"/>
       <c r="B45" s="22"/>
       <c r="C45" s="13" t="s">
         <v>53</v>
@@ -1973,7 +1973,7 @@
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="31"/>
+      <c r="A46" s="27"/>
       <c r="B46" s="22"/>
       <c r="C46" s="13" t="s">
         <v>54</v>
@@ -1986,8 +1986,8 @@
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="31"/>
-      <c r="B47" s="23"/>
+      <c r="A47" s="27"/>
+      <c r="B47" s="39"/>
       <c r="C47" s="13" t="s">
         <v>65</v>
       </c>
@@ -1999,8 +1999,8 @@
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="31"/>
-      <c r="B48" s="24" t="s">
+      <c r="A48" s="27"/>
+      <c r="B48" s="23" t="s">
         <v>58</v>
       </c>
       <c r="C48" s="11" t="s">
@@ -2014,8 +2014,8 @@
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="31"/>
-      <c r="B49" s="25"/>
+      <c r="A49" s="27"/>
+      <c r="B49" s="24"/>
       <c r="C49" s="11" t="s">
         <v>57</v>
       </c>
@@ -2027,8 +2027,8 @@
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="31"/>
-      <c r="B50" s="25"/>
+      <c r="A50" s="27"/>
+      <c r="B50" s="24"/>
       <c r="C50" s="11" t="s">
         <v>59</v>
       </c>
@@ -2040,8 +2040,8 @@
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="31"/>
-      <c r="B51" s="25"/>
+      <c r="A51" s="27"/>
+      <c r="B51" s="24"/>
       <c r="C51" s="11" t="s">
         <v>60</v>
       </c>
@@ -2053,8 +2053,8 @@
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="31"/>
-      <c r="B52" s="25"/>
+      <c r="A52" s="27"/>
+      <c r="B52" s="24"/>
       <c r="C52" s="11" t="s">
         <v>61</v>
       </c>
@@ -2066,8 +2066,8 @@
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="31"/>
-      <c r="B53" s="25"/>
+      <c r="A53" s="27"/>
+      <c r="B53" s="24"/>
       <c r="C53" s="11" t="s">
         <v>62</v>
       </c>
@@ -2079,8 +2079,8 @@
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="31"/>
-      <c r="B54" s="26"/>
+      <c r="A54" s="27"/>
+      <c r="B54" s="25"/>
       <c r="C54" s="11" t="s">
         <v>64</v>
       </c>
@@ -2092,7 +2092,7 @@
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="31"/>
+      <c r="A55" s="27"/>
       <c r="B55" s="21" t="s">
         <v>66</v>
       </c>
@@ -2107,7 +2107,7 @@
       </c>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="31"/>
+      <c r="A56" s="27"/>
       <c r="B56" s="22"/>
       <c r="C56" s="13" t="s">
         <v>68</v>
@@ -2120,7 +2120,7 @@
       </c>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="31"/>
+      <c r="A57" s="27"/>
       <c r="B57" s="22"/>
       <c r="C57" s="13" t="s">
         <v>69</v>
@@ -2133,7 +2133,7 @@
       </c>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="31"/>
+      <c r="A58" s="27"/>
       <c r="B58" s="22"/>
       <c r="C58" s="13" t="s">
         <v>70</v>
@@ -2146,7 +2146,7 @@
       </c>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="31"/>
+      <c r="A59" s="27"/>
       <c r="B59" s="22"/>
       <c r="C59" s="13" t="s">
         <v>63</v>
@@ -2159,7 +2159,7 @@
       </c>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="31"/>
+      <c r="A60" s="27"/>
       <c r="B60" s="22"/>
       <c r="C60" s="13" t="s">
         <v>71</v>
@@ -2172,8 +2172,8 @@
       </c>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="31"/>
-      <c r="B61" s="23"/>
+      <c r="A61" s="27"/>
+      <c r="B61" s="39"/>
       <c r="C61" s="13" t="s">
         <v>55</v>
       </c>
@@ -2185,8 +2185,8 @@
       </c>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="31"/>
-      <c r="B62" s="24" t="s">
+      <c r="A62" s="27"/>
+      <c r="B62" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="11" t="s">
@@ -2200,8 +2200,8 @@
       </c>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="31"/>
-      <c r="B63" s="25"/>
+      <c r="A63" s="27"/>
+      <c r="B63" s="24"/>
       <c r="C63" s="11" t="s">
         <v>73</v>
       </c>
@@ -2213,8 +2213,8 @@
       </c>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="31"/>
-      <c r="B64" s="25"/>
+      <c r="A64" s="27"/>
+      <c r="B64" s="24"/>
       <c r="C64" s="11" t="s">
         <v>74</v>
       </c>
@@ -2226,8 +2226,8 @@
       </c>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="31"/>
-      <c r="B65" s="25"/>
+      <c r="A65" s="27"/>
+      <c r="B65" s="24"/>
       <c r="C65" s="11" t="s">
         <v>75</v>
       </c>
@@ -2239,8 +2239,8 @@
       </c>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="31"/>
-      <c r="B66" s="25"/>
+      <c r="A66" s="27"/>
+      <c r="B66" s="24"/>
       <c r="C66" s="11" t="s">
         <v>76</v>
       </c>
@@ -2252,8 +2252,8 @@
       </c>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="31"/>
-      <c r="B67" s="25"/>
+      <c r="A67" s="27"/>
+      <c r="B67" s="24"/>
       <c r="C67" s="11" t="s">
         <v>78</v>
       </c>
@@ -2265,8 +2265,8 @@
       </c>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="31"/>
-      <c r="B68" s="25"/>
+      <c r="A68" s="27"/>
+      <c r="B68" s="24"/>
       <c r="C68" s="11" t="s">
         <v>77</v>
       </c>
@@ -2278,8 +2278,8 @@
       </c>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="31"/>
-      <c r="B69" s="25"/>
+      <c r="A69" s="27"/>
+      <c r="B69" s="24"/>
       <c r="C69" s="11" t="s">
         <v>83</v>
       </c>
@@ -2291,8 +2291,8 @@
       </c>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="31"/>
-      <c r="B70" s="25"/>
+      <c r="A70" s="27"/>
+      <c r="B70" s="24"/>
       <c r="C70" s="11" t="s">
         <v>84</v>
       </c>
@@ -2304,8 +2304,8 @@
       </c>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="31"/>
-      <c r="B71" s="25"/>
+      <c r="A71" s="27"/>
+      <c r="B71" s="24"/>
       <c r="C71" s="11" t="s">
         <v>120</v>
       </c>
@@ -2317,8 +2317,8 @@
       </c>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="31"/>
-      <c r="B72" s="26"/>
+      <c r="A72" s="27"/>
+      <c r="B72" s="25"/>
       <c r="C72" s="11" t="s">
         <v>79</v>
       </c>
@@ -2330,7 +2330,7 @@
       </c>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="31"/>
+      <c r="A73" s="27"/>
       <c r="B73" s="21" t="s">
         <v>95</v>
       </c>
@@ -2345,7 +2345,7 @@
       </c>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="31"/>
+      <c r="A74" s="27"/>
       <c r="B74" s="22"/>
       <c r="C74" s="13" t="s">
         <v>98</v>
@@ -2358,8 +2358,8 @@
       </c>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="31"/>
-      <c r="B75" s="23"/>
+      <c r="A75" s="27"/>
+      <c r="B75" s="39"/>
       <c r="C75" s="13" t="s">
         <v>97</v>
       </c>
@@ -2371,53 +2371,53 @@
       </c>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="34"/>
-      <c r="B76" s="24" t="s">
+      <c r="A76" s="28"/>
+      <c r="B76" s="23" t="s">
         <v>87</v>
       </c>
       <c r="C76" s="11" t="s">
         <v>88</v>
       </c>
       <c r="D76" s="20" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E76" s="17" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="34"/>
-      <c r="B77" s="25"/>
+      <c r="A77" s="28"/>
+      <c r="B77" s="24"/>
       <c r="C77" s="11"/>
       <c r="D77" s="15"/>
       <c r="E77" s="17"/>
     </row>
     <row r="78" spans="1:5">
-      <c r="A78" s="34"/>
-      <c r="B78" s="25"/>
+      <c r="A78" s="28"/>
+      <c r="B78" s="24"/>
       <c r="C78" s="11"/>
       <c r="D78" s="15"/>
       <c r="E78" s="17"/>
     </row>
     <row r="79" spans="1:5">
-      <c r="A79" s="34"/>
-      <c r="B79" s="25"/>
+      <c r="A79" s="28"/>
+      <c r="B79" s="24"/>
       <c r="C79" s="11"/>
       <c r="D79" s="15"/>
       <c r="E79" s="17"/>
     </row>
     <row r="80" spans="1:5">
-      <c r="A80" s="35"/>
-      <c r="B80" s="26"/>
+      <c r="A80" s="29"/>
+      <c r="B80" s="25"/>
       <c r="C80" s="11"/>
       <c r="D80" s="15"/>
       <c r="E80" s="17"/>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="36" t="s">
+      <c r="A81" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="B81" s="39"/>
+      <c r="B81" s="33"/>
       <c r="C81" s="9" t="s">
         <v>90</v>
       </c>
@@ -2429,8 +2429,8 @@
       </c>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="37"/>
-      <c r="B82" s="40"/>
+      <c r="A82" s="31"/>
+      <c r="B82" s="34"/>
       <c r="C82" s="9" t="s">
         <v>112</v>
       </c>
@@ -2442,8 +2442,8 @@
       </c>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="37"/>
-      <c r="B83" s="40"/>
+      <c r="A83" s="31"/>
+      <c r="B83" s="34"/>
       <c r="C83" s="9" t="s">
         <v>86</v>
       </c>
@@ -2455,8 +2455,8 @@
       </c>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="37"/>
-      <c r="B84" s="40"/>
+      <c r="A84" s="31"/>
+      <c r="B84" s="34"/>
       <c r="C84" s="9" t="s">
         <v>89</v>
       </c>
@@ -2468,20 +2468,20 @@
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="38"/>
-      <c r="B85" s="41"/>
+      <c r="A85" s="32"/>
+      <c r="B85" s="35"/>
       <c r="C85" s="9" t="s">
         <v>99</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E85" s="17" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="30" t="s">
+      <c r="A86" s="37" t="s">
         <v>82</v>
       </c>
       <c r="B86" s="6" t="s">
@@ -2498,7 +2498,7 @@
       </c>
     </row>
     <row r="87" spans="1:5">
-      <c r="A87" s="31"/>
+      <c r="A87" s="27"/>
       <c r="B87" s="6" t="s">
         <v>92</v>
       </c>
@@ -2513,7 +2513,7 @@
       </c>
     </row>
     <row r="88" spans="1:5">
-      <c r="A88" s="31"/>
+      <c r="A88" s="27"/>
       <c r="B88" s="6" t="s">
         <v>93</v>
       </c>
@@ -2528,7 +2528,7 @@
       </c>
     </row>
     <row r="89" spans="1:5">
-      <c r="A89" s="31"/>
+      <c r="A89" s="27"/>
       <c r="B89" s="6" t="s">
         <v>94</v>
       </c>
@@ -2543,7 +2543,7 @@
       </c>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="31"/>
+      <c r="A90" s="27"/>
       <c r="B90" s="6" t="s">
         <v>101</v>
       </c>
@@ -2558,7 +2558,7 @@
       </c>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="31"/>
+      <c r="A91" s="27"/>
       <c r="B91" s="6" t="s">
         <v>102</v>
       </c>
@@ -2573,7 +2573,7 @@
       </c>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="32"/>
+      <c r="A92" s="38"/>
       <c r="B92" s="6" t="s">
         <v>100</v>
       </c>
@@ -2604,12 +2604,7 @@
   </sheetData>
   <autoFilter ref="A2:E92"/>
   <mergeCells count="18">
-    <mergeCell ref="B25:B36"/>
-    <mergeCell ref="B76:B80"/>
-    <mergeCell ref="A3:A80"/>
-    <mergeCell ref="A81:A85"/>
-    <mergeCell ref="B81:B85"/>
-    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A86:A92"/>
     <mergeCell ref="B73:B75"/>
     <mergeCell ref="B37:B40"/>
@@ -2617,11 +2612,16 @@
     <mergeCell ref="B48:B54"/>
     <mergeCell ref="B55:B61"/>
     <mergeCell ref="B62:B72"/>
+    <mergeCell ref="B25:B36"/>
+    <mergeCell ref="B76:B80"/>
+    <mergeCell ref="A3:A80"/>
+    <mergeCell ref="A81:A85"/>
+    <mergeCell ref="B81:B85"/>
+    <mergeCell ref="B3:B7"/>
     <mergeCell ref="B8:B10"/>
     <mergeCell ref="B11:B17"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="B20:B24"/>
-    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/01.需求特性/版本特性列表.xlsx
+++ b/internal_doc/01.需求特性/版本特性列表.xlsx
@@ -12,14 +12,14 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">版本特性表!$A$2:$E$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">版本特性表!$A$2:$F$93</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="125">
   <si>
     <t>内容项</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -502,6 +502,22 @@
   </si>
   <si>
     <t>SNMP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>热备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>英文描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hot-spare Node</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>√</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -992,63 +1008,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1057,6 +1016,63 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1360,25 +1376,27 @@
   <sheetPr codeName="Sheet1">
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.5" customWidth="1"/>
     <col min="2" max="2" width="15.375" customWidth="1"/>
     <col min="3" max="3" width="40.125" customWidth="1"/>
-    <col min="4" max="5" width="18.625" customWidth="1"/>
+    <col min="4" max="4" width="18.75" customWidth="1"/>
+    <col min="5" max="6" width="18.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
+      <c r="A1" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="42"/>
-    </row>
-    <row r="2" spans="1:5" ht="26.25" customHeight="1" thickBot="1">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="23"/>
+    </row>
+    <row r="2" spans="1:6" ht="26.25" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1388,1240 +1406,1353 @@
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="14.25" thickTop="1">
-      <c r="A3" s="26" t="s">
+    <row r="3" spans="1:6" ht="14.25" thickTop="1">
+      <c r="A3" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="42" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="27"/>
-      <c r="B4" s="24"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="25"/>
+      <c r="B4" s="31"/>
       <c r="C4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="27"/>
-      <c r="B5" s="24"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="25"/>
+      <c r="B5" s="31"/>
       <c r="C5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="27"/>
-      <c r="B6" s="24"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="25"/>
+      <c r="B6" s="31"/>
       <c r="C6" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="27"/>
-      <c r="B7" s="25"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="25"/>
+      <c r="B7" s="32"/>
       <c r="C7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="E7" s="17" t="s">
+      <c r="D7" s="11"/>
+      <c r="E7" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="F7" s="17" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="27"/>
-      <c r="B8" s="21" t="s">
+    <row r="8" spans="1:6">
+      <c r="A8" s="25"/>
+      <c r="B8" s="27" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="13"/>
+      <c r="E8" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="F8" s="17" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="27"/>
-      <c r="B9" s="22"/>
+    <row r="9" spans="1:6">
+      <c r="A9" s="25"/>
+      <c r="B9" s="28"/>
       <c r="C9" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="14"/>
+      <c r="E9" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="F9" s="17" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="27"/>
-      <c r="B10" s="39"/>
+    <row r="10" spans="1:6">
+      <c r="A10" s="25"/>
+      <c r="B10" s="29"/>
       <c r="C10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="13"/>
+      <c r="E10" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="F10" s="17" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="27"/>
-      <c r="B11" s="23" t="s">
+    <row r="11" spans="1:6">
+      <c r="A11" s="25"/>
+      <c r="B11" s="30" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="D11" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="27"/>
-      <c r="B12" s="24"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="25"/>
+      <c r="B12" s="31"/>
       <c r="C12" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="27"/>
-      <c r="B13" s="24"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="25"/>
+      <c r="B13" s="31"/>
       <c r="C13" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="27"/>
-      <c r="B14" s="24"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="25"/>
+      <c r="B14" s="31"/>
       <c r="C14" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="27"/>
-      <c r="B15" s="24"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="25"/>
+      <c r="B15" s="31"/>
       <c r="C15" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="27"/>
-      <c r="B16" s="24"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="25"/>
+      <c r="B16" s="31"/>
       <c r="C16" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="27"/>
-      <c r="B17" s="25"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="25"/>
+      <c r="B17" s="31"/>
       <c r="C17" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="25"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="27"/>
-      <c r="B18" s="21" t="s">
+      <c r="D18" s="11"/>
+      <c r="E18" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="25"/>
+      <c r="B19" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C19" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="27"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="13" t="s">
+      <c r="D19" s="13"/>
+      <c r="E19" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="25"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="27"/>
-      <c r="B20" s="23" t="s">
+      <c r="D20" s="13"/>
+      <c r="E20" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="25"/>
+      <c r="B21" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C21" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="27"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="11" t="s">
+      <c r="D21" s="11"/>
+      <c r="E21" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="25"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="27"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="11" t="s">
+      <c r="D22" s="11"/>
+      <c r="E22" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="25"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="27"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="11" t="s">
+      <c r="D23" s="11"/>
+      <c r="E23" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="25"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="27"/>
-      <c r="B24" s="25"/>
-      <c r="C24" s="11" t="s">
+      <c r="D24" s="11"/>
+      <c r="E24" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="25"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="27"/>
-      <c r="B25" s="21" t="s">
+      <c r="D25" s="11"/>
+      <c r="E25" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="25"/>
+      <c r="B26" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C26" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="27"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="13" t="s">
+      <c r="D26" s="13"/>
+      <c r="E26" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="25"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D26" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="27"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="13" t="s">
+      <c r="D27" s="13"/>
+      <c r="E27" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="25"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="27"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="13" t="s">
+      <c r="D28" s="13"/>
+      <c r="E28" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="25"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D28" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="27"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="13" t="s">
+      <c r="D29" s="13"/>
+      <c r="E29" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="25"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="27"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="13" t="s">
+      <c r="D30" s="13"/>
+      <c r="E30" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="25"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D30" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="27"/>
-      <c r="B31" s="22"/>
-      <c r="C31" s="13" t="s">
+      <c r="D31" s="13"/>
+      <c r="E31" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="25"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D31" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="27"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="13" t="s">
+      <c r="D32" s="13"/>
+      <c r="E32" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="25"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="27"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="13" t="s">
+      <c r="D33" s="13"/>
+      <c r="E33" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="25"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D33" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="27"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="13" t="s">
+      <c r="D34" s="13"/>
+      <c r="E34" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F34" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="25"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D34" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="27"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="13" t="s">
+      <c r="D35" s="13"/>
+      <c r="E35" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="25"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="D35" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E35" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="27"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="13" t="s">
+      <c r="D36" s="13"/>
+      <c r="E36" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="25"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="27"/>
-      <c r="B37" s="23" t="s">
+      <c r="D37" s="13"/>
+      <c r="E37" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="25"/>
+      <c r="B38" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C38" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D37" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="27"/>
-      <c r="B38" s="24"/>
-      <c r="C38" s="11" t="s">
+      <c r="D38" s="11"/>
+      <c r="E38" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="25"/>
+      <c r="B39" s="31"/>
+      <c r="C39" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D38" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E38" s="17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="27"/>
-      <c r="B39" s="24"/>
-      <c r="C39" s="11" t="s">
+      <c r="D39" s="11"/>
+      <c r="E39" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="25"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="D39" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E39" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="27"/>
-      <c r="B40" s="25"/>
-      <c r="C40" s="11" t="s">
+      <c r="D40" s="11"/>
+      <c r="E40" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="25"/>
+      <c r="B41" s="32"/>
+      <c r="C41" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="D40" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="27"/>
-      <c r="B41" s="21" t="s">
+      <c r="D41" s="11"/>
+      <c r="E41" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="25"/>
+      <c r="B42" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C42" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E41" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="27"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="13" t="s">
+      <c r="D42" s="13"/>
+      <c r="E42" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="25"/>
+      <c r="B43" s="28"/>
+      <c r="C43" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E42" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="27"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="13" t="s">
+      <c r="D43" s="13"/>
+      <c r="E43" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="25"/>
+      <c r="B44" s="28"/>
+      <c r="C44" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E43" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="27"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="13" t="s">
+      <c r="D44" s="13"/>
+      <c r="E44" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="25"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D44" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E44" s="17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="27"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="13" t="s">
+      <c r="D45" s="13"/>
+      <c r="E45" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="25"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D45" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E45" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="27"/>
-      <c r="B46" s="22"/>
-      <c r="C46" s="13" t="s">
+      <c r="D46" s="13"/>
+      <c r="E46" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F46" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="25"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D46" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E46" s="17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="27"/>
-      <c r="B47" s="39"/>
-      <c r="C47" s="13" t="s">
+      <c r="D47" s="13"/>
+      <c r="E47" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="25"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D47" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E47" s="17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="27"/>
-      <c r="B48" s="23" t="s">
+      <c r="D48" s="13"/>
+      <c r="E48" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F48" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="25"/>
+      <c r="B49" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C49" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D48" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E48" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="27"/>
-      <c r="B49" s="24"/>
-      <c r="C49" s="11" t="s">
+      <c r="D49" s="11"/>
+      <c r="E49" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F49" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="25"/>
+      <c r="B50" s="31"/>
+      <c r="C50" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D49" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E49" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="27"/>
-      <c r="B50" s="24"/>
-      <c r="C50" s="11" t="s">
+      <c r="D50" s="11"/>
+      <c r="E50" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F50" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="25"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D50" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E50" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="27"/>
-      <c r="B51" s="24"/>
-      <c r="C51" s="11" t="s">
+      <c r="D51" s="11"/>
+      <c r="E51" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F51" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="25"/>
+      <c r="B52" s="31"/>
+      <c r="C52" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D51" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E51" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="27"/>
-      <c r="B52" s="24"/>
-      <c r="C52" s="11" t="s">
+      <c r="D52" s="11"/>
+      <c r="E52" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F52" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="25"/>
+      <c r="B53" s="31"/>
+      <c r="C53" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D52" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E52" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="27"/>
-      <c r="B53" s="24"/>
-      <c r="C53" s="11" t="s">
+      <c r="D53" s="11"/>
+      <c r="E53" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F53" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="25"/>
+      <c r="B54" s="31"/>
+      <c r="C54" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D53" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E53" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="27"/>
-      <c r="B54" s="25"/>
-      <c r="C54" s="11" t="s">
+      <c r="D54" s="11"/>
+      <c r="E54" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F54" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="25"/>
+      <c r="B55" s="32"/>
+      <c r="C55" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D54" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E54" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="27"/>
-      <c r="B55" s="21" t="s">
+      <c r="D55" s="11"/>
+      <c r="E55" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F55" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="25"/>
+      <c r="B56" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="C56" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="D55" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E55" s="17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="27"/>
-      <c r="B56" s="22"/>
-      <c r="C56" s="13" t="s">
+      <c r="D56" s="13"/>
+      <c r="E56" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F56" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="25"/>
+      <c r="B57" s="28"/>
+      <c r="C57" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D56" s="20" t="s">
+      <c r="D57" s="13"/>
+      <c r="E57" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="E56" s="17" t="s">
+      <c r="F57" s="17" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="27"/>
-      <c r="B57" s="22"/>
-      <c r="C57" s="13" t="s">
+    <row r="58" spans="1:6">
+      <c r="A58" s="25"/>
+      <c r="B58" s="28"/>
+      <c r="C58" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="D57" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E57" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="27"/>
-      <c r="B58" s="22"/>
-      <c r="C58" s="13" t="s">
+      <c r="D58" s="13"/>
+      <c r="E58" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F58" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="25"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D58" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E58" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="27"/>
-      <c r="B59" s="22"/>
-      <c r="C59" s="13" t="s">
+      <c r="D59" s="13"/>
+      <c r="E59" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F59" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="25"/>
+      <c r="B60" s="28"/>
+      <c r="C60" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D59" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E59" s="17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="27"/>
-      <c r="B60" s="22"/>
-      <c r="C60" s="13" t="s">
+      <c r="D60" s="13"/>
+      <c r="E60" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F60" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="25"/>
+      <c r="B61" s="28"/>
+      <c r="C61" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="D60" s="20" t="s">
+      <c r="D61" s="13"/>
+      <c r="E61" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="E60" s="17" t="s">
+      <c r="F61" s="17" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="27"/>
-      <c r="B61" s="39"/>
-      <c r="C61" s="13" t="s">
+    <row r="62" spans="1:6">
+      <c r="A62" s="25"/>
+      <c r="B62" s="29"/>
+      <c r="C62" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D61" s="20" t="s">
+      <c r="D62" s="13"/>
+      <c r="E62" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="E61" s="17" t="s">
+      <c r="F62" s="17" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="27"/>
-      <c r="B62" s="23" t="s">
+    <row r="63" spans="1:6">
+      <c r="A63" s="25"/>
+      <c r="B63" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C63" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E62" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="27"/>
-      <c r="B63" s="24"/>
-      <c r="C63" s="11" t="s">
+      <c r="D63" s="11"/>
+      <c r="E63" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F63" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="25"/>
+      <c r="B64" s="31"/>
+      <c r="C64" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E63" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="27"/>
-      <c r="B64" s="24"/>
-      <c r="C64" s="11" t="s">
+      <c r="D64" s="11"/>
+      <c r="E64" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F64" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="25"/>
+      <c r="B65" s="31"/>
+      <c r="C65" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D64" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E64" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="27"/>
-      <c r="B65" s="24"/>
-      <c r="C65" s="11" t="s">
+      <c r="D65" s="11"/>
+      <c r="E65" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F65" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="25"/>
+      <c r="B66" s="31"/>
+      <c r="C66" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="D65" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E65" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="27"/>
-      <c r="B66" s="24"/>
-      <c r="C66" s="11" t="s">
+      <c r="D66" s="11"/>
+      <c r="E66" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F66" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="25"/>
+      <c r="B67" s="31"/>
+      <c r="C67" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D66" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E66" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="27"/>
-      <c r="B67" s="24"/>
-      <c r="C67" s="11" t="s">
+      <c r="D67" s="11"/>
+      <c r="E67" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F67" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="25"/>
+      <c r="B68" s="31"/>
+      <c r="C68" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="D67" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E67" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="27"/>
-      <c r="B68" s="24"/>
-      <c r="C68" s="11" t="s">
+      <c r="D68" s="11"/>
+      <c r="E68" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F68" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="25"/>
+      <c r="B69" s="31"/>
+      <c r="C69" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="D68" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E68" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="27"/>
-      <c r="B69" s="24"/>
-      <c r="C69" s="11" t="s">
+      <c r="D69" s="11"/>
+      <c r="E69" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F69" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="25"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="D69" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E69" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="27"/>
-      <c r="B70" s="24"/>
-      <c r="C70" s="11" t="s">
+      <c r="D70" s="11"/>
+      <c r="E70" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F70" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="25"/>
+      <c r="B71" s="31"/>
+      <c r="C71" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="D70" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E70" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="27"/>
-      <c r="B71" s="24"/>
-      <c r="C71" s="11" t="s">
+      <c r="D71" s="11"/>
+      <c r="E71" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F71" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="25"/>
+      <c r="B72" s="31"/>
+      <c r="C72" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="D71" s="20" t="s">
+      <c r="D72" s="11"/>
+      <c r="E72" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="E71" s="17" t="s">
+      <c r="F72" s="17" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="27"/>
-      <c r="B72" s="25"/>
-      <c r="C72" s="11" t="s">
+    <row r="73" spans="1:6">
+      <c r="A73" s="25"/>
+      <c r="B73" s="32"/>
+      <c r="C73" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D72" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E72" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="27"/>
-      <c r="B73" s="21" t="s">
+      <c r="D73" s="11"/>
+      <c r="E73" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F73" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" s="25"/>
+      <c r="B74" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="C73" s="13" t="s">
+      <c r="C74" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="D73" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E73" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="27"/>
-      <c r="B74" s="22"/>
-      <c r="C74" s="13" t="s">
+      <c r="D74" s="13"/>
+      <c r="E74" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F74" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" s="25"/>
+      <c r="B75" s="28"/>
+      <c r="C75" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="D74" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E74" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="27"/>
-      <c r="B75" s="39"/>
-      <c r="C75" s="13" t="s">
+      <c r="D75" s="13"/>
+      <c r="E75" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F75" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" s="25"/>
+      <c r="B76" s="29"/>
+      <c r="C76" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D75" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E75" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="28"/>
-      <c r="B76" s="23" t="s">
+      <c r="D76" s="13"/>
+      <c r="E76" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F76" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" s="34"/>
+      <c r="B77" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="C77" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="D76" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="E76" s="17" t="s">
+      <c r="D77" s="11"/>
+      <c r="E77" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="F77" s="17" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="28"/>
-      <c r="B77" s="24"/>
-      <c r="C77" s="11"/>
-      <c r="D77" s="15"/>
-      <c r="E77" s="17"/>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="28"/>
-      <c r="B78" s="24"/>
+    <row r="78" spans="1:6">
+      <c r="A78" s="34"/>
+      <c r="B78" s="31"/>
       <c r="C78" s="11"/>
-      <c r="D78" s="15"/>
-      <c r="E78" s="17"/>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="28"/>
-      <c r="B79" s="24"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="17"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="34"/>
+      <c r="B79" s="31"/>
       <c r="C79" s="11"/>
-      <c r="D79" s="15"/>
-      <c r="E79" s="17"/>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="29"/>
-      <c r="B80" s="25"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="15"/>
+      <c r="F79" s="17"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="34"/>
+      <c r="B80" s="31"/>
       <c r="C80" s="11"/>
-      <c r="D80" s="15"/>
-      <c r="E80" s="17"/>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="30" t="s">
+      <c r="D80" s="11"/>
+      <c r="E80" s="15"/>
+      <c r="F80" s="17"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" s="35"/>
+      <c r="B81" s="32"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="15"/>
+      <c r="F81" s="17"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="B81" s="33"/>
-      <c r="C81" s="9" t="s">
+      <c r="B82" s="39"/>
+      <c r="C82" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D81" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E81" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="31"/>
-      <c r="B82" s="34"/>
-      <c r="C82" s="9" t="s">
+      <c r="D82" s="9"/>
+      <c r="E82" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F82" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" s="37"/>
+      <c r="B83" s="40"/>
+      <c r="C83" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="D82" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E82" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="31"/>
-      <c r="B83" s="34"/>
-      <c r="C83" s="9" t="s">
+      <c r="D83" s="9"/>
+      <c r="E83" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F83" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" s="37"/>
+      <c r="B84" s="40"/>
+      <c r="C84" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E83" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="31"/>
-      <c r="B84" s="34"/>
-      <c r="C84" s="9" t="s">
+      <c r="D84" s="9"/>
+      <c r="E84" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F84" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="37"/>
+      <c r="B85" s="40"/>
+      <c r="C85" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="D84" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E84" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="32"/>
-      <c r="B85" s="35"/>
-      <c r="C85" s="9" t="s">
+      <c r="D85" s="9"/>
+      <c r="E85" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F85" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" s="38"/>
+      <c r="B86" s="41"/>
+      <c r="C86" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="D85" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E85" s="17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="37" t="s">
+      <c r="D86" s="9"/>
+      <c r="E86" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F86" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="B86" s="6" t="s">
+      <c r="B87" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C86" s="9" t="s">
+      <c r="C87" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="D86" s="20" t="s">
+      <c r="D87" s="9"/>
+      <c r="E87" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="E86" s="17" t="s">
+      <c r="F87" s="17" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="27"/>
-      <c r="B87" s="6" t="s">
+    <row r="88" spans="1:6">
+      <c r="A88" s="25"/>
+      <c r="B88" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C87" s="9" t="s">
+      <c r="C88" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="D87" s="20" t="s">
+      <c r="D88" s="9"/>
+      <c r="E88" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="E87" s="17" t="s">
+      <c r="F88" s="17" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="27"/>
-      <c r="B88" s="6" t="s">
+    <row r="89" spans="1:6">
+      <c r="A89" s="25"/>
+      <c r="B89" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C88" s="9" t="s">
+      <c r="C89" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="D88" s="20" t="s">
+      <c r="D89" s="9"/>
+      <c r="E89" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="E88" s="17" t="s">
+      <c r="F89" s="17" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
-      <c r="A89" s="27"/>
-      <c r="B89" s="6" t="s">
+    <row r="90" spans="1:6">
+      <c r="A90" s="25"/>
+      <c r="B90" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C89" s="9" t="s">
+      <c r="C90" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D89" s="20" t="s">
+      <c r="D90" s="9"/>
+      <c r="E90" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="E89" s="17" t="s">
+      <c r="F90" s="17" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="27"/>
-      <c r="B90" s="6" t="s">
+    <row r="91" spans="1:6">
+      <c r="A91" s="25"/>
+      <c r="B91" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="C90" s="9" t="s">
+      <c r="C91" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="D90" s="20" t="s">
+      <c r="D91" s="9"/>
+      <c r="E91" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="E90" s="17" t="s">
+      <c r="F91" s="17" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
-      <c r="A91" s="27"/>
-      <c r="B91" s="6" t="s">
+    <row r="92" spans="1:6">
+      <c r="A92" s="25"/>
+      <c r="B92" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C91" s="9" t="s">
+      <c r="C92" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="D91" s="20" t="s">
+      <c r="D92" s="9"/>
+      <c r="E92" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="E91" s="17" t="s">
+      <c r="F92" s="17" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
-      <c r="A92" s="38"/>
-      <c r="B92" s="6" t="s">
+    <row r="93" spans="1:6">
+      <c r="A93" s="26"/>
+      <c r="B93" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C92" s="9" t="s">
+      <c r="C93" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="D92" s="20" t="s">
+      <c r="D93" s="9"/>
+      <c r="E93" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="E92" s="17" t="s">
+      <c r="F93" s="17" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
-      <c r="A93" s="5"/>
-      <c r="B93" s="6"/>
-      <c r="C93" s="9"/>
-      <c r="D93" s="15"/>
-      <c r="E93" s="17"/>
-    </row>
-    <row r="94" spans="1:5" ht="14.25" thickBot="1">
-      <c r="A94" s="7"/>
-      <c r="B94" s="8"/>
-      <c r="C94" s="10"/>
-      <c r="D94" s="18"/>
-      <c r="E94" s="19"/>
+    <row r="94" spans="1:6">
+      <c r="A94" s="5"/>
+      <c r="B94" s="6"/>
+      <c r="C94" s="9"/>
+      <c r="D94" s="9"/>
+      <c r="E94" s="15"/>
+      <c r="F94" s="17"/>
+    </row>
+    <row r="95" spans="1:6" ht="14.25" thickBot="1">
+      <c r="A95" s="7"/>
+      <c r="B95" s="8"/>
+      <c r="C95" s="10"/>
+      <c r="D95" s="10"/>
+      <c r="E95" s="18"/>
+      <c r="F95" s="19"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E92"/>
+  <autoFilter ref="A2:F93">
+    <filterColumn colId="3"/>
+  </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A86:A92"/>
-    <mergeCell ref="B73:B75"/>
-    <mergeCell ref="B37:B40"/>
-    <mergeCell ref="B41:B47"/>
-    <mergeCell ref="B48:B54"/>
-    <mergeCell ref="B55:B61"/>
-    <mergeCell ref="B62:B72"/>
-    <mergeCell ref="B25:B36"/>
-    <mergeCell ref="B76:B80"/>
-    <mergeCell ref="A3:A80"/>
-    <mergeCell ref="A81:A85"/>
-    <mergeCell ref="B81:B85"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B21:B25"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A87:A93"/>
+    <mergeCell ref="B74:B76"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B42:B48"/>
+    <mergeCell ref="B49:B55"/>
+    <mergeCell ref="B56:B62"/>
+    <mergeCell ref="B63:B73"/>
+    <mergeCell ref="B26:B37"/>
+    <mergeCell ref="B77:B81"/>
+    <mergeCell ref="A3:A81"/>
+    <mergeCell ref="A82:A86"/>
+    <mergeCell ref="B82:B86"/>
     <mergeCell ref="B3:B7"/>
     <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B20:B24"/>
+    <mergeCell ref="B11:B18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/01.需求特性/版本特性列表.xlsx
+++ b/internal_doc/01.需求特性/版本特性列表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="128">
   <si>
     <t>内容项</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -514,6 +514,18 @@
   </si>
   <si>
     <t>Hot-spare Node</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>√</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作审计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>√</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1008,6 +1020,21 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1026,22 +1053,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1387,14 +1399,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="28"/>
     </row>
     <row r="2" spans="1:6" ht="26.25" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="s">
@@ -1435,8 +1447,8 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="25"/>
-      <c r="B4" s="31"/>
+      <c r="A4" s="30"/>
+      <c r="B4" s="24"/>
       <c r="C4" s="12" t="s">
         <v>17</v>
       </c>
@@ -1449,8 +1461,8 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="25"/>
-      <c r="B5" s="31"/>
+      <c r="A5" s="30"/>
+      <c r="B5" s="24"/>
       <c r="C5" s="11" t="s">
         <v>18</v>
       </c>
@@ -1463,8 +1475,8 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="25"/>
-      <c r="B6" s="31"/>
+      <c r="A6" s="30"/>
+      <c r="B6" s="24"/>
       <c r="C6" s="11" t="s">
         <v>19</v>
       </c>
@@ -1477,8 +1489,8 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="25"/>
-      <c r="B7" s="32"/>
+      <c r="A7" s="30"/>
+      <c r="B7" s="25"/>
       <c r="C7" s="11" t="s">
         <v>20</v>
       </c>
@@ -1491,8 +1503,8 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="25"/>
-      <c r="B8" s="27" t="s">
+      <c r="A8" s="30"/>
+      <c r="B8" s="21" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="13" t="s">
@@ -1507,8 +1519,8 @@
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="25"/>
-      <c r="B9" s="28"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="32"/>
       <c r="C9" s="14" t="s">
         <v>22</v>
       </c>
@@ -1521,8 +1533,8 @@
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="25"/>
-      <c r="B10" s="29"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="22"/>
       <c r="C10" s="13" t="s">
         <v>23</v>
       </c>
@@ -1535,8 +1547,8 @@
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="25"/>
-      <c r="B11" s="30" t="s">
+      <c r="A11" s="30"/>
+      <c r="B11" s="23" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="11" t="s">
@@ -1551,8 +1563,8 @@
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="25"/>
-      <c r="B12" s="31"/>
+      <c r="A12" s="30"/>
+      <c r="B12" s="24"/>
       <c r="C12" s="11" t="s">
         <v>45</v>
       </c>
@@ -1565,8 +1577,8 @@
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="25"/>
-      <c r="B13" s="31"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="24"/>
       <c r="C13" s="11" t="s">
         <v>46</v>
       </c>
@@ -1579,8 +1591,8 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="25"/>
-      <c r="B14" s="31"/>
+      <c r="A14" s="30"/>
+      <c r="B14" s="24"/>
       <c r="C14" s="11" t="s">
         <v>24</v>
       </c>
@@ -1593,8 +1605,8 @@
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="25"/>
-      <c r="B15" s="31"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="24"/>
       <c r="C15" s="11" t="s">
         <v>25</v>
       </c>
@@ -1607,8 +1619,8 @@
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="25"/>
-      <c r="B16" s="31"/>
+      <c r="A16" s="30"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="11" t="s">
         <v>110</v>
       </c>
@@ -1621,8 +1633,8 @@
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="25"/>
-      <c r="B17" s="31"/>
+      <c r="A17" s="30"/>
+      <c r="B17" s="24"/>
       <c r="C17" s="11" t="s">
         <v>121</v>
       </c>
@@ -1637,8 +1649,8 @@
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="25"/>
-      <c r="B18" s="32"/>
+      <c r="A18" s="30"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="11" t="s">
         <v>26</v>
       </c>
@@ -1651,8 +1663,8 @@
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="25"/>
-      <c r="B19" s="27" t="s">
+      <c r="A19" s="30"/>
+      <c r="B19" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="13" t="s">
@@ -1667,8 +1679,8 @@
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="25"/>
-      <c r="B20" s="29"/>
+      <c r="A20" s="30"/>
+      <c r="B20" s="22"/>
       <c r="C20" s="13" t="s">
         <v>28</v>
       </c>
@@ -1681,8 +1693,8 @@
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="25"/>
-      <c r="B21" s="30" t="s">
+      <c r="A21" s="30"/>
+      <c r="B21" s="23" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="11" t="s">
@@ -1697,8 +1709,8 @@
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="25"/>
-      <c r="B22" s="31"/>
+      <c r="A22" s="30"/>
+      <c r="B22" s="24"/>
       <c r="C22" s="11" t="s">
         <v>30</v>
       </c>
@@ -1711,8 +1723,8 @@
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="25"/>
-      <c r="B23" s="31"/>
+      <c r="A23" s="30"/>
+      <c r="B23" s="24"/>
       <c r="C23" s="11" t="s">
         <v>31</v>
       </c>
@@ -1725,8 +1737,8 @@
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="25"/>
-      <c r="B24" s="31"/>
+      <c r="A24" s="30"/>
+      <c r="B24" s="24"/>
       <c r="C24" s="11" t="s">
         <v>32</v>
       </c>
@@ -1739,8 +1751,8 @@
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="25"/>
-      <c r="B25" s="32"/>
+      <c r="A25" s="30"/>
+      <c r="B25" s="25"/>
       <c r="C25" s="11" t="s">
         <v>33</v>
       </c>
@@ -1753,8 +1765,8 @@
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="25"/>
-      <c r="B26" s="27" t="s">
+      <c r="A26" s="30"/>
+      <c r="B26" s="21" t="s">
         <v>13</v>
       </c>
       <c r="C26" s="13" t="s">
@@ -1769,8 +1781,8 @@
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="25"/>
-      <c r="B27" s="28"/>
+      <c r="A27" s="30"/>
+      <c r="B27" s="32"/>
       <c r="C27" s="13" t="s">
         <v>39</v>
       </c>
@@ -1783,8 +1795,8 @@
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="25"/>
-      <c r="B28" s="28"/>
+      <c r="A28" s="30"/>
+      <c r="B28" s="32"/>
       <c r="C28" s="13" t="s">
         <v>15</v>
       </c>
@@ -1797,8 +1809,8 @@
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="25"/>
-      <c r="B29" s="28"/>
+      <c r="A29" s="30"/>
+      <c r="B29" s="32"/>
       <c r="C29" s="13" t="s">
         <v>41</v>
       </c>
@@ -1811,8 +1823,8 @@
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="25"/>
-      <c r="B30" s="28"/>
+      <c r="A30" s="30"/>
+      <c r="B30" s="32"/>
       <c r="C30" s="13" t="s">
         <v>40</v>
       </c>
@@ -1825,8 +1837,8 @@
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="25"/>
-      <c r="B31" s="28"/>
+      <c r="A31" s="30"/>
+      <c r="B31" s="32"/>
       <c r="C31" s="13" t="s">
         <v>43</v>
       </c>
@@ -1839,8 +1851,8 @@
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="25"/>
-      <c r="B32" s="28"/>
+      <c r="A32" s="30"/>
+      <c r="B32" s="32"/>
       <c r="C32" s="13" t="s">
         <v>34</v>
       </c>
@@ -1853,8 +1865,8 @@
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="25"/>
-      <c r="B33" s="28"/>
+      <c r="A33" s="30"/>
+      <c r="B33" s="32"/>
       <c r="C33" s="13" t="s">
         <v>35</v>
       </c>
@@ -1867,8 +1879,8 @@
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="25"/>
-      <c r="B34" s="28"/>
+      <c r="A34" s="30"/>
+      <c r="B34" s="32"/>
       <c r="C34" s="13" t="s">
         <v>36</v>
       </c>
@@ -1881,8 +1893,8 @@
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="25"/>
-      <c r="B35" s="28"/>
+      <c r="A35" s="30"/>
+      <c r="B35" s="32"/>
       <c r="C35" s="13" t="s">
         <v>37</v>
       </c>
@@ -1895,8 +1907,8 @@
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="25"/>
-      <c r="B36" s="28"/>
+      <c r="A36" s="30"/>
+      <c r="B36" s="32"/>
       <c r="C36" s="13" t="s">
         <v>111</v>
       </c>
@@ -1909,8 +1921,8 @@
       </c>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="25"/>
-      <c r="B37" s="28"/>
+      <c r="A37" s="30"/>
+      <c r="B37" s="32"/>
       <c r="C37" s="13" t="s">
         <v>38</v>
       </c>
@@ -1923,8 +1935,8 @@
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="25"/>
-      <c r="B38" s="30" t="s">
+      <c r="A38" s="30"/>
+      <c r="B38" s="23" t="s">
         <v>44</v>
       </c>
       <c r="C38" s="11" t="s">
@@ -1939,8 +1951,8 @@
       </c>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="25"/>
-      <c r="B39" s="31"/>
+      <c r="A39" s="30"/>
+      <c r="B39" s="24"/>
       <c r="C39" s="11" t="s">
         <v>47</v>
       </c>
@@ -1953,8 +1965,8 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="25"/>
-      <c r="B40" s="31"/>
+      <c r="A40" s="30"/>
+      <c r="B40" s="24"/>
       <c r="C40" s="11" t="s">
         <v>48</v>
       </c>
@@ -1967,8 +1979,8 @@
       </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="25"/>
-      <c r="B41" s="32"/>
+      <c r="A41" s="30"/>
+      <c r="B41" s="25"/>
       <c r="C41" s="11" t="s">
         <v>80</v>
       </c>
@@ -1981,8 +1993,8 @@
       </c>
     </row>
     <row r="42" spans="1:6">
-      <c r="A42" s="25"/>
-      <c r="B42" s="27" t="s">
+      <c r="A42" s="30"/>
+      <c r="B42" s="21" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="13" t="s">
@@ -1997,8 +2009,8 @@
       </c>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="25"/>
-      <c r="B43" s="28"/>
+      <c r="A43" s="30"/>
+      <c r="B43" s="32"/>
       <c r="C43" s="13" t="s">
         <v>50</v>
       </c>
@@ -2011,8 +2023,8 @@
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="25"/>
-      <c r="B44" s="28"/>
+      <c r="A44" s="30"/>
+      <c r="B44" s="32"/>
       <c r="C44" s="13" t="s">
         <v>51</v>
       </c>
@@ -2025,8 +2037,8 @@
       </c>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45" s="25"/>
-      <c r="B45" s="28"/>
+      <c r="A45" s="30"/>
+      <c r="B45" s="32"/>
       <c r="C45" s="13" t="s">
         <v>52</v>
       </c>
@@ -2039,8 +2051,8 @@
       </c>
     </row>
     <row r="46" spans="1:6">
-      <c r="A46" s="25"/>
-      <c r="B46" s="28"/>
+      <c r="A46" s="30"/>
+      <c r="B46" s="32"/>
       <c r="C46" s="13" t="s">
         <v>53</v>
       </c>
@@ -2053,8 +2065,8 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="A47" s="25"/>
-      <c r="B47" s="28"/>
+      <c r="A47" s="30"/>
+      <c r="B47" s="32"/>
       <c r="C47" s="13" t="s">
         <v>54</v>
       </c>
@@ -2067,8 +2079,8 @@
       </c>
     </row>
     <row r="48" spans="1:6">
-      <c r="A48" s="25"/>
-      <c r="B48" s="29"/>
+      <c r="A48" s="30"/>
+      <c r="B48" s="22"/>
       <c r="C48" s="13" t="s">
         <v>65</v>
       </c>
@@ -2081,8 +2093,8 @@
       </c>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="25"/>
-      <c r="B49" s="30" t="s">
+      <c r="A49" s="30"/>
+      <c r="B49" s="23" t="s">
         <v>58</v>
       </c>
       <c r="C49" s="11" t="s">
@@ -2097,8 +2109,8 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="25"/>
-      <c r="B50" s="31"/>
+      <c r="A50" s="30"/>
+      <c r="B50" s="24"/>
       <c r="C50" s="11" t="s">
         <v>57</v>
       </c>
@@ -2111,8 +2123,8 @@
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="25"/>
-      <c r="B51" s="31"/>
+      <c r="A51" s="30"/>
+      <c r="B51" s="24"/>
       <c r="C51" s="11" t="s">
         <v>59</v>
       </c>
@@ -2125,8 +2137,8 @@
       </c>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="25"/>
-      <c r="B52" s="31"/>
+      <c r="A52" s="30"/>
+      <c r="B52" s="24"/>
       <c r="C52" s="11" t="s">
         <v>60</v>
       </c>
@@ -2139,8 +2151,8 @@
       </c>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="25"/>
-      <c r="B53" s="31"/>
+      <c r="A53" s="30"/>
+      <c r="B53" s="24"/>
       <c r="C53" s="11" t="s">
         <v>61</v>
       </c>
@@ -2153,8 +2165,8 @@
       </c>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="25"/>
-      <c r="B54" s="31"/>
+      <c r="A54" s="30"/>
+      <c r="B54" s="24"/>
       <c r="C54" s="11" t="s">
         <v>62</v>
       </c>
@@ -2167,8 +2179,8 @@
       </c>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="25"/>
-      <c r="B55" s="32"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="25"/>
       <c r="C55" s="11" t="s">
         <v>64</v>
       </c>
@@ -2181,8 +2193,8 @@
       </c>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="25"/>
-      <c r="B56" s="27" t="s">
+      <c r="A56" s="30"/>
+      <c r="B56" s="21" t="s">
         <v>66</v>
       </c>
       <c r="C56" s="13" t="s">
@@ -2197,8 +2209,8 @@
       </c>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="25"/>
-      <c r="B57" s="28"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="32"/>
       <c r="C57" s="13" t="s">
         <v>68</v>
       </c>
@@ -2211,8 +2223,8 @@
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="25"/>
-      <c r="B58" s="28"/>
+      <c r="A58" s="30"/>
+      <c r="B58" s="32"/>
       <c r="C58" s="13" t="s">
         <v>69</v>
       </c>
@@ -2225,8 +2237,8 @@
       </c>
     </row>
     <row r="59" spans="1:6">
-      <c r="A59" s="25"/>
-      <c r="B59" s="28"/>
+      <c r="A59" s="30"/>
+      <c r="B59" s="32"/>
       <c r="C59" s="13" t="s">
         <v>70</v>
       </c>
@@ -2239,8 +2251,8 @@
       </c>
     </row>
     <row r="60" spans="1:6">
-      <c r="A60" s="25"/>
-      <c r="B60" s="28"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="32"/>
       <c r="C60" s="13" t="s">
         <v>63</v>
       </c>
@@ -2253,8 +2265,8 @@
       </c>
     </row>
     <row r="61" spans="1:6">
-      <c r="A61" s="25"/>
-      <c r="B61" s="28"/>
+      <c r="A61" s="30"/>
+      <c r="B61" s="32"/>
       <c r="C61" s="13" t="s">
         <v>71</v>
       </c>
@@ -2267,8 +2279,8 @@
       </c>
     </row>
     <row r="62" spans="1:6">
-      <c r="A62" s="25"/>
-      <c r="B62" s="29"/>
+      <c r="A62" s="30"/>
+      <c r="B62" s="22"/>
       <c r="C62" s="13" t="s">
         <v>55</v>
       </c>
@@ -2281,8 +2293,8 @@
       </c>
     </row>
     <row r="63" spans="1:6">
-      <c r="A63" s="25"/>
-      <c r="B63" s="30" t="s">
+      <c r="A63" s="30"/>
+      <c r="B63" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="11" t="s">
@@ -2297,8 +2309,8 @@
       </c>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="25"/>
-      <c r="B64" s="31"/>
+      <c r="A64" s="30"/>
+      <c r="B64" s="24"/>
       <c r="C64" s="11" t="s">
         <v>73</v>
       </c>
@@ -2311,8 +2323,8 @@
       </c>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="25"/>
-      <c r="B65" s="31"/>
+      <c r="A65" s="30"/>
+      <c r="B65" s="24"/>
       <c r="C65" s="11" t="s">
         <v>74</v>
       </c>
@@ -2325,8 +2337,8 @@
       </c>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="25"/>
-      <c r="B66" s="31"/>
+      <c r="A66" s="30"/>
+      <c r="B66" s="24"/>
       <c r="C66" s="11" t="s">
         <v>75</v>
       </c>
@@ -2339,8 +2351,8 @@
       </c>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="25"/>
-      <c r="B67" s="31"/>
+      <c r="A67" s="30"/>
+      <c r="B67" s="24"/>
       <c r="C67" s="11" t="s">
         <v>76</v>
       </c>
@@ -2353,8 +2365,8 @@
       </c>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="25"/>
-      <c r="B68" s="31"/>
+      <c r="A68" s="30"/>
+      <c r="B68" s="24"/>
       <c r="C68" s="11" t="s">
         <v>78</v>
       </c>
@@ -2367,8 +2379,8 @@
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="25"/>
-      <c r="B69" s="31"/>
+      <c r="A69" s="30"/>
+      <c r="B69" s="24"/>
       <c r="C69" s="11" t="s">
         <v>77</v>
       </c>
@@ -2381,8 +2393,8 @@
       </c>
     </row>
     <row r="70" spans="1:6">
-      <c r="A70" s="25"/>
-      <c r="B70" s="31"/>
+      <c r="A70" s="30"/>
+      <c r="B70" s="24"/>
       <c r="C70" s="11" t="s">
         <v>83</v>
       </c>
@@ -2395,8 +2407,8 @@
       </c>
     </row>
     <row r="71" spans="1:6">
-      <c r="A71" s="25"/>
-      <c r="B71" s="31"/>
+      <c r="A71" s="30"/>
+      <c r="B71" s="24"/>
       <c r="C71" s="11" t="s">
         <v>84</v>
       </c>
@@ -2409,8 +2421,8 @@
       </c>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="25"/>
-      <c r="B72" s="31"/>
+      <c r="A72" s="30"/>
+      <c r="B72" s="24"/>
       <c r="C72" s="11" t="s">
         <v>120</v>
       </c>
@@ -2423,8 +2435,8 @@
       </c>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="25"/>
-      <c r="B73" s="32"/>
+      <c r="A73" s="30"/>
+      <c r="B73" s="25"/>
       <c r="C73" s="11" t="s">
         <v>79</v>
       </c>
@@ -2437,8 +2449,8 @@
       </c>
     </row>
     <row r="74" spans="1:6">
-      <c r="A74" s="25"/>
-      <c r="B74" s="27" t="s">
+      <c r="A74" s="30"/>
+      <c r="B74" s="21" t="s">
         <v>95</v>
       </c>
       <c r="C74" s="13" t="s">
@@ -2453,8 +2465,8 @@
       </c>
     </row>
     <row r="75" spans="1:6">
-      <c r="A75" s="25"/>
-      <c r="B75" s="28"/>
+      <c r="A75" s="30"/>
+      <c r="B75" s="32"/>
       <c r="C75" s="13" t="s">
         <v>98</v>
       </c>
@@ -2467,14 +2479,14 @@
       </c>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="25"/>
-      <c r="B76" s="29"/>
+      <c r="A76" s="30"/>
+      <c r="B76" s="22"/>
       <c r="C76" s="13" t="s">
         <v>97</v>
       </c>
       <c r="D76" s="13"/>
       <c r="E76" s="15" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="F76" s="17" t="s">
         <v>113</v>
@@ -2482,7 +2494,7 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="34"/>
-      <c r="B77" s="30" t="s">
+      <c r="B77" s="23" t="s">
         <v>87</v>
       </c>
       <c r="C77" s="11" t="s">
@@ -2498,15 +2510,21 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="34"/>
-      <c r="B78" s="31"/>
-      <c r="C78" s="11"/>
+      <c r="B78" s="24"/>
+      <c r="C78" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="D78" s="11"/>
-      <c r="E78" s="15"/>
-      <c r="F78" s="17"/>
+      <c r="E78" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="F78" s="17" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="34"/>
-      <c r="B79" s="31"/>
+      <c r="B79" s="24"/>
       <c r="C79" s="11"/>
       <c r="D79" s="11"/>
       <c r="E79" s="15"/>
@@ -2514,7 +2532,7 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="34"/>
-      <c r="B80" s="31"/>
+      <c r="B80" s="24"/>
       <c r="C80" s="11"/>
       <c r="D80" s="11"/>
       <c r="E80" s="15"/>
@@ -2522,7 +2540,7 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="35"/>
-      <c r="B81" s="32"/>
+      <c r="B81" s="25"/>
       <c r="C81" s="11"/>
       <c r="D81" s="11"/>
       <c r="E81" s="15"/>
@@ -2601,7 +2619,7 @@
       </c>
     </row>
     <row r="87" spans="1:6">
-      <c r="A87" s="24" t="s">
+      <c r="A87" s="29" t="s">
         <v>82</v>
       </c>
       <c r="B87" s="6" t="s">
@@ -2619,7 +2637,7 @@
       </c>
     </row>
     <row r="88" spans="1:6">
-      <c r="A88" s="25"/>
+      <c r="A88" s="30"/>
       <c r="B88" s="6" t="s">
         <v>92</v>
       </c>
@@ -2635,7 +2653,7 @@
       </c>
     </row>
     <row r="89" spans="1:6">
-      <c r="A89" s="25"/>
+      <c r="A89" s="30"/>
       <c r="B89" s="6" t="s">
         <v>93</v>
       </c>
@@ -2651,7 +2669,7 @@
       </c>
     </row>
     <row r="90" spans="1:6">
-      <c r="A90" s="25"/>
+      <c r="A90" s="30"/>
       <c r="B90" s="6" t="s">
         <v>94</v>
       </c>
@@ -2667,7 +2685,7 @@
       </c>
     </row>
     <row r="91" spans="1:6">
-      <c r="A91" s="25"/>
+      <c r="A91" s="30"/>
       <c r="B91" s="6" t="s">
         <v>101</v>
       </c>
@@ -2683,7 +2701,7 @@
       </c>
     </row>
     <row r="92" spans="1:6">
-      <c r="A92" s="25"/>
+      <c r="A92" s="30"/>
       <c r="B92" s="6" t="s">
         <v>102</v>
       </c>
@@ -2699,7 +2717,7 @@
       </c>
     </row>
     <row r="93" spans="1:6">
-      <c r="A93" s="26"/>
+      <c r="A93" s="31"/>
       <c r="B93" s="6" t="s">
         <v>100</v>
       </c>
@@ -2735,6 +2753,8 @@
     <filterColumn colId="3"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B18"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="B21:B25"/>
     <mergeCell ref="A1:F1"/>
@@ -2751,8 +2771,6 @@
     <mergeCell ref="A82:A86"/>
     <mergeCell ref="B82:B86"/>
     <mergeCell ref="B3:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
